--- a/test-data/aws-secrets-expected-values.xlsx
+++ b/test-data/aws-secrets-expected-values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30BFCB44-B603-4FD9-82EE-AE122EF127DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{77595F4A-3E19-43DE-87DD-05A3E8235F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="East" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="569">
   <si>
     <t>Secret key</t>
   </si>
@@ -1667,7 +1667,43 @@
     <t>pby-shopx-qa-usw2-db-rds-cluster.cluster-ciq1we1ad8ex.us-west-2.rds.amazonaws.com</t>
   </si>
   <si>
+    <t>https://sqs.us-west-2.amazonaws.com/714179603964/pby-shopx-qa-sqs-user-activity</t>
+  </si>
+  <si>
+    <t>arn:aws:sns:us-west-2:714179603964:pby-shopx-qa-usw2-msg-informative-topic</t>
+  </si>
+  <si>
+    <t>arn:aws:sns:us-west-2:714179603964:pby-shopx-qa-usw2-msg-actionable-topic</t>
+  </si>
+  <si>
+    <t>https://sqs.us-west-2.amazonaws.com/714179603964/pby-shopx-qa-usw2-msg-actionable-queue-dlq</t>
+  </si>
+  <si>
+    <t>https://sqs.us-west-2.amazonaws.com/714179603964/pby-shopx-qa-usw2-msg-informative-queue-dlq</t>
+  </si>
+  <si>
+    <t>https://sqs.us-west-2.amazonaws.com/714179603964/pby-shopx-qa-usw2-msg-actionable-queue</t>
+  </si>
+  <si>
+    <t>https://sqs.us-west-2.amazonaws.com/714179603964/pby-shopx-qa-usw2-msg-informative-queue</t>
+  </si>
+  <si>
     <t>master.pby-shopx-qa-usw2-cache-valkey-rg.1mkdiz.usw2.cache.amazonaws.com</t>
+  </si>
+  <si>
+    <t>us-west-2</t>
+  </si>
+  <si>
+    <t>pby-shopx-qa-usw2-msg-actionable-queue</t>
+  </si>
+  <si>
+    <t>pby-shopx-qa-usw2-msg-informative-queue</t>
+  </si>
+  <si>
+    <t>https://api-poc-dev.auth.us-west-2.amazoncognito.com/oauth2/token</t>
+  </si>
+  <si>
+    <t>arn:aws:sns:us-west-2:714179603964:pby-shopx-qa-usw2-msg-workorder-events</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1710,7 +1746,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1729,6 +1765,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -1791,10 +1833,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1810,8 +1853,11 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -5063,8 +5109,8 @@
       <c r="A64" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B64" s="8" t="s">
-        <v>109</v>
+      <c r="B64" s="9" t="s">
+        <v>544</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -5312,7 +5358,7 @@
         <v>165</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>166</v>
+        <v>545</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -5320,23 +5366,23 @@
         <v>167</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>168</v>
+        <v>546</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B97" s="6" t="s">
-        <v>170</v>
+      <c r="B97" s="10" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B98" s="8" t="s">
-        <v>172</v>
+      <c r="B98" s="9" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -5623,8 +5669,8 @@
       <c r="A134" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="B134" s="8" t="s">
-        <v>239</v>
+      <c r="B134" s="9" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -5647,8 +5693,8 @@
       <c r="A137" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="B137" s="6" t="s">
-        <v>245</v>
+      <c r="B137" s="10" t="s">
+        <v>550</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -5736,7 +5782,7 @@
         <v>261</v>
       </c>
       <c r="B148" s="8" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -5792,7 +5838,7 @@
         <v>272</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>273</v>
+        <v>552</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -5840,7 +5886,7 @@
         <v>280</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>281</v>
+        <v>553</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -5848,7 +5894,7 @@
         <v>282</v>
       </c>
       <c r="B162" s="8" t="s">
-        <v>283</v>
+        <v>554</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -6055,8 +6101,8 @@
       <c r="A188" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="B188" s="8" t="s">
-        <v>331</v>
+      <c r="B188" s="9" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -6668,7 +6714,7 @@
         <v>461</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>462</v>
+        <v>556</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -7120,6 +7166,14 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B64" r:id="rId1" xr:uid="{E9C70401-8988-41D0-B02B-69CC00C5476F}"/>
+    <hyperlink ref="B97" r:id="rId2" xr:uid="{AF3EB40E-441A-4C42-A37B-89BB5B89BD82}"/>
+    <hyperlink ref="B98" r:id="rId3" xr:uid="{B4F445CF-C9C0-488A-B27B-006CCEE95ED6}"/>
+    <hyperlink ref="B134" r:id="rId4" xr:uid="{1867D7CC-DE25-4EB4-A293-A1CADC5E0AEA}"/>
+    <hyperlink ref="B137" r:id="rId5" xr:uid="{2748A3FE-CC8F-4D47-9884-62EB1AD2E5F4}"/>
+    <hyperlink ref="B188" r:id="rId6" xr:uid="{9316ED0A-94B5-4F32-B2B5-B03D0D26ACF9}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7135,50 +7189,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="B2" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="B3" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="B4" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="B5" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="B6" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
     </row>
   </sheetData>

--- a/test-data/aws-secrets-expected-values.xlsx
+++ b/test-data/aws-secrets-expected-values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30230"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E79F5D6-3653-49F8-A76C-46E56028A99A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D993C6E6-8BF9-4604-90F7-A258549EACD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="East" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="505">
   <si>
     <t>Secret key</t>
   </si>
@@ -1512,24 +1512,6 @@
   </si>
   <si>
     <t>pby-shopx-qa-usw2-app-pos-generated-log-post-processing-s3</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>0.3</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>10000</t>
-  </si>
-  <si>
-    <t>5000</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1572,7 +1554,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1586,11 +1568,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Carlito"/>
     </font>
     <font>
@@ -1618,7 +1595,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1633,12 +1610,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
     <fill>
@@ -1762,9 +1733,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1776,61 +1747,57 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2032,2474 +1999,2474 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="16.5">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.5">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16.5">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16.5">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="5">
         <v>5432</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16.5">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="12" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="13" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="16.5">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="12" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="16.5">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17.25">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="15" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="11" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17.25">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="15" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="15" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17.25">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="20"/>
+      <c r="B17" s="16"/>
     </row>
     <row r="18" spans="1:2" ht="17.25">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="20"/>
+      <c r="B18" s="16"/>
     </row>
     <row r="19" spans="1:2" ht="17.25">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="20"/>
+      <c r="B19" s="16"/>
     </row>
     <row r="20" spans="1:2" ht="17.25">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="36">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="19"/>
+      <c r="B21" s="15"/>
     </row>
     <row r="22" spans="1:2" ht="16.5">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="5" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17.25">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="11" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="16.5">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.6">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17.25">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="12" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="10"/>
-      <c r="B27" s="15"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="11"/>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="10"/>
-      <c r="B28" s="15"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="11"/>
     </row>
     <row r="29" spans="1:2" ht="17.25">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="19"/>
+      <c r="B29" s="15"/>
     </row>
     <row r="30" spans="1:2" ht="17.25">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="17.25">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="17.25">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="17.25">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="17.25">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="17.25">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="17.25">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B36" s="21"/>
+      <c r="B36" s="17"/>
     </row>
     <row r="37" spans="1:2" ht="17.25">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="11" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="17.25">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="15" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="17.25">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B39" s="18" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="17.25">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="11" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="17.25">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="11" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="17.25">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="11" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="17.25">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B43" s="19" t="s">
+      <c r="B43" s="15" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="17.25">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="15" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="36">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="11" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="36">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="36">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="36">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="B48" s="11" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="36">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B49" s="15" t="s">
+      <c r="B49" s="11" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="17.25">
-      <c r="A50" s="10" t="s">
+      <c r="A50" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="15" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="17.25">
-      <c r="A51" s="10" t="s">
+      <c r="A51" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B51" s="19" t="s">
+      <c r="B51" s="15" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="17.25">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B52" s="19">
+      <c r="B52" s="15">
         <v>3600</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="17.25">
-      <c r="A53" s="10" t="s">
+      <c r="A53" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B53" s="19">
+      <c r="B53" s="15">
         <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="17.25">
-      <c r="A54" s="10" t="s">
+      <c r="A54" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="15" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="17.25">
-      <c r="A55" s="10" t="s">
+      <c r="A55" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="19">
+      <c r="B55" s="15">
         <v>3600</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="17.25">
-      <c r="A56" s="10" t="s">
+      <c r="A56" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B56" s="19">
+      <c r="B56" s="15">
         <v>30</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="17.25">
-      <c r="A57" s="10" t="s">
+      <c r="A57" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B57" s="11" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="17.25">
-      <c r="A58" s="10" t="s">
+      <c r="A58" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="11" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="17.25">
-      <c r="A59" s="10" t="s">
+      <c r="A59" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B59" s="19">
+      <c r="B59" s="15">
         <v>3660</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="17.25">
-      <c r="A60" s="10" t="s">
+      <c r="A60" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B60" s="19" t="s">
+      <c r="B60" s="15" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="17.25">
-      <c r="A61" s="10" t="s">
+      <c r="A61" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B61" s="15" t="s">
+      <c r="B61" s="11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="17.25">
-      <c r="A62" s="10" t="s">
+      <c r="A62" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B62" s="19">
+      <c r="B62" s="15">
         <v>600</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="17.25">
-      <c r="A63" s="10" t="s">
+      <c r="A63" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B63" s="19">
+      <c r="B63" s="15">
         <v>60000</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="17.25">
-      <c r="A64" s="10" t="s">
+      <c r="A64" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B64" s="19">
+      <c r="B64" s="15">
         <v>60000</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="17.25">
-      <c r="A65" s="10" t="s">
+      <c r="A65" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B65" s="19">
+      <c r="B65" s="15">
         <v>3660</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="17.25">
-      <c r="A66" s="10" t="s">
+      <c r="A66" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B66" s="19">
+      <c r="B66" s="15">
         <v>3600</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="16.5">
-      <c r="A67" s="13" t="s">
+      <c r="A67" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B67" s="13" t="s">
+      <c r="B67" s="9" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="17.25">
-      <c r="A68" s="10" t="s">
+      <c r="A68" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B68" s="15" t="s">
+      <c r="B68" s="11" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="17.25">
-      <c r="A69" s="10" t="s">
+      <c r="A69" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B69" s="19" t="s">
+      <c r="B69" s="15" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="17.25">
-      <c r="A70" s="10" t="s">
+      <c r="A70" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B70" s="19" t="s">
+      <c r="B70" s="15" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="17.25">
-      <c r="A71" s="10" t="s">
+      <c r="A71" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B71" s="19" t="s">
+      <c r="B71" s="15" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="17.25">
-      <c r="A72" s="10" t="s">
+      <c r="A72" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B72" s="19">
+      <c r="B72" s="15">
         <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="17.25">
-      <c r="A73" s="10" t="s">
+      <c r="A73" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B73" s="19" t="s">
+      <c r="B73" s="15" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="17.25">
-      <c r="A74" s="10" t="s">
+      <c r="A74" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B74" s="19" t="s">
+      <c r="B74" s="15" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="17.25">
-      <c r="A75" s="10" t="s">
+      <c r="A75" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B75" s="23" t="s">
+      <c r="B75" s="19" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="17.25">
-      <c r="A76" s="10" t="s">
+      <c r="A76" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B76" s="19" t="s">
+      <c r="B76" s="15" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="17.25">
-      <c r="A77" s="10" t="s">
+      <c r="A77" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B77" s="19">
+      <c r="B77" s="15">
         <v>10000</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="17.25">
-      <c r="A78" s="10" t="s">
+      <c r="A78" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B78" s="19" t="s">
+      <c r="B78" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="17.25">
-      <c r="A79" s="10" t="s">
+      <c r="A79" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="B79" s="19" t="s">
+      <c r="B79" s="15" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="17.25">
-      <c r="A80" s="10" t="s">
+      <c r="A80" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B80" s="19">
+      <c r="B80" s="15">
         <v>5000</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="17.25">
-      <c r="A81" s="10" t="s">
+      <c r="A81" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B81" s="19">
+      <c r="B81" s="15">
         <v>30</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="17.25">
-      <c r="A82" s="10" t="s">
+      <c r="A82" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B82" s="19" t="s">
+      <c r="B82" s="15" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="17.25">
-      <c r="A83" s="10" t="s">
+      <c r="A83" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B83" s="19">
+      <c r="B83" s="15">
         <v>8000</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="17.25">
-      <c r="A84" s="10" t="s">
+      <c r="A84" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B84" s="19" t="s">
+      <c r="B84" s="15" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="85" spans="1:2" ht="17.25">
-      <c r="A85" s="10" t="s">
+      <c r="A85" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B85" s="19">
+      <c r="B85" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:2" ht="17.25">
-      <c r="A86" s="10" t="s">
+      <c r="A86" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="B86" s="19" t="s">
+      <c r="B86" s="15" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="33.75">
-      <c r="A87" s="10" t="s">
+      <c r="A87" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B87" s="15" t="s">
+      <c r="B87" s="11" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="88" spans="1:2" ht="17.25">
-      <c r="A88" s="10" t="s">
+      <c r="A88" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B88" s="19">
+      <c r="B88" s="15">
         <v>262144</v>
       </c>
     </row>
     <row r="89" spans="1:2" ht="16.5">
-      <c r="A89" s="9" t="s">
+      <c r="A89" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B89" s="9" t="s">
+      <c r="B89" s="5" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="90" spans="1:2" ht="16.5">
-      <c r="A90" s="9" t="s">
+      <c r="A90" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B90" s="9" t="s">
+      <c r="B90" s="5" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="33.75">
-      <c r="A91" s="9" t="s">
+      <c r="A91" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B91" s="13" t="s">
+      <c r="B91" s="9" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="33.75">
-      <c r="A92" s="13" t="s">
+      <c r="A92" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B92" s="13" t="s">
+      <c r="B92" s="9" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="93" spans="1:2" ht="17.25">
-      <c r="A93" s="10" t="s">
+      <c r="A93" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B93" s="19" t="s">
+      <c r="B93" s="15" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="94" spans="1:2" ht="17.25">
-      <c r="A94" s="10" t="s">
+      <c r="A94" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="B94" s="19" t="s">
+      <c r="B94" s="15" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="17.25">
-      <c r="A95" s="10" t="s">
+      <c r="A95" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B95" s="19" t="s">
+      <c r="B95" s="15" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="17.25">
-      <c r="A96" s="10" t="s">
+      <c r="A96" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B96" s="19" t="s">
+      <c r="B96" s="15" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="17.25">
-      <c r="A97" s="10" t="s">
+      <c r="A97" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B97" s="19" t="s">
+      <c r="B97" s="15" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="98" spans="1:2" ht="17.25">
-      <c r="A98" s="10" t="s">
+      <c r="A98" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B98" s="19" t="s">
+      <c r="B98" s="15" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="17.25">
-      <c r="A99" s="10" t="s">
+      <c r="A99" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="11" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="100" spans="1:2" ht="17.25">
-      <c r="A100" s="10" t="s">
+      <c r="A100" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="B100" s="19" t="s">
+      <c r="B100" s="15" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="17.25">
-      <c r="A101" s="10" t="s">
+      <c r="A101" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B101" s="19" t="s">
+      <c r="B101" s="15" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="102" spans="1:2" ht="36">
-      <c r="A102" s="10" t="s">
+      <c r="A102" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B102" s="19" t="s">
+      <c r="B102" s="15" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="103" spans="1:2" ht="36">
-      <c r="A103" s="10" t="s">
+      <c r="A103" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="B103" s="19" t="s">
+      <c r="B103" s="15" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="104" spans="1:2" ht="17.25">
-      <c r="A104" s="10" t="s">
+      <c r="A104" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="B104" s="19" t="s">
+      <c r="B104" s="15" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="105" spans="1:2" ht="17.25">
-      <c r="A105" s="10" t="s">
+      <c r="A105" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B105" s="19" t="s">
+      <c r="B105" s="15" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="106" spans="1:2" ht="17.25">
-      <c r="A106" s="10" t="s">
+      <c r="A106" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B106" s="19" t="s">
+      <c r="B106" s="15" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="107" spans="1:2" ht="17.25">
-      <c r="A107" s="10" t="s">
+      <c r="A107" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B107" s="19" t="s">
+      <c r="B107" s="15" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="108" spans="1:2" ht="17.25">
-      <c r="A108" s="10" t="s">
+      <c r="A108" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B108" s="19" t="s">
+      <c r="B108" s="15" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="109" spans="1:2" ht="17.25">
-      <c r="A109" s="10" t="s">
+      <c r="A109" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="B109" s="19" t="s">
+      <c r="B109" s="15" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="110" spans="1:2" ht="17.25">
-      <c r="A110" s="10" t="s">
+      <c r="A110" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="B110" s="19" t="s">
+      <c r="B110" s="15" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="111" spans="1:2" ht="17.25">
-      <c r="A111" s="10" t="s">
+      <c r="A111" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B111" s="19" t="s">
+      <c r="B111" s="15" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="112" spans="1:2" ht="17.25">
-      <c r="A112" s="10" t="s">
+      <c r="A112" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B112" s="19" t="s">
+      <c r="B112" s="15" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="113" spans="1:2" ht="17.25">
-      <c r="A113" s="10" t="s">
+      <c r="A113" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B113" s="19" t="s">
+      <c r="B113" s="15" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="114" spans="1:2" ht="17.25">
-      <c r="A114" s="10" t="s">
+      <c r="A114" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="B114" s="19" t="s">
+      <c r="B114" s="15" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="115" spans="1:2" ht="17.25">
-      <c r="A115" s="10" t="s">
+      <c r="A115" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B115" s="19" t="b">
+      <c r="B115" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:2" ht="17.25">
-      <c r="A116" s="10" t="s">
+      <c r="A116" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B116" s="15" t="s">
+      <c r="B116" s="11" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="117" spans="1:2" ht="17.25">
-      <c r="A117" s="10" t="s">
+      <c r="A117" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="B117" s="19" t="s">
+      <c r="B117" s="15" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="118" spans="1:2" ht="17.25">
-      <c r="A118" s="10" t="s">
+      <c r="A118" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="B118" s="19">
+      <c r="B118" s="15">
         <v>12013553177</v>
       </c>
     </row>
     <row r="119" spans="1:2" ht="17.25">
-      <c r="A119" s="10" t="s">
+      <c r="A119" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="B119" s="19" t="b">
+      <c r="B119" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:2" ht="16.5">
-      <c r="A120" s="13" t="s">
+      <c r="A120" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="B120" s="13" t="s">
+      <c r="B120" s="9" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="121" spans="1:2" ht="17.25">
-      <c r="A121" s="10" t="s">
+      <c r="A121" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="B121" s="19" t="b">
+      <c r="B121" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:2" ht="17.25">
-      <c r="A122" s="10" t="s">
+      <c r="A122" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="B122" s="15" t="s">
+      <c r="B122" s="11" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="123" spans="1:2" ht="17.25">
-      <c r="A123" s="10" t="s">
+      <c r="A123" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="B123" s="19" t="s">
+      <c r="B123" s="15" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="124" spans="1:2" ht="17.25">
-      <c r="A124" s="10" t="s">
+      <c r="A124" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="B124" s="19" t="s">
+      <c r="B124" s="15" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="125" spans="1:2" ht="17.25">
-      <c r="A125" s="10" t="s">
+      <c r="A125" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="B125" s="19">
+      <c r="B125" s="15">
         <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:2" ht="33.75">
-      <c r="A126" s="13" t="s">
+      <c r="A126" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="B126" s="13" t="s">
+      <c r="B126" s="9" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="127" spans="1:2" ht="17.25">
-      <c r="A127" s="10" t="s">
+      <c r="A127" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B127" s="19" t="s">
+      <c r="B127" s="15" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="128" spans="1:2" ht="17.25">
-      <c r="A128" s="10" t="s">
+      <c r="A128" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B128" s="19" t="s">
+      <c r="B128" s="15" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="129" spans="1:2" ht="33.75">
-      <c r="A129" s="13" t="s">
+      <c r="A129" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="B129" s="13" t="s">
+      <c r="B129" s="9" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="130" spans="1:2" ht="17.25">
-      <c r="A130" s="10" t="s">
+      <c r="A130" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="B130" s="19" t="s">
+      <c r="B130" s="15" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="131" spans="1:2" ht="17.25">
-      <c r="A131" s="10" t="s">
+      <c r="A131" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="B131" s="19" t="s">
+      <c r="B131" s="15" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="132" spans="1:2" ht="17.25">
-      <c r="A132" s="10" t="s">
+      <c r="A132" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="B132" s="19" t="s">
+      <c r="B132" s="15" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="133" spans="1:2" ht="17.25">
-      <c r="A133" s="10" t="s">
+      <c r="A133" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="B133" s="19">
+      <c r="B133" s="15">
         <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:2" ht="17.25">
-      <c r="A134" s="10" t="s">
+      <c r="A134" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="B134" s="19">
+      <c r="B134" s="15">
         <v>2000</v>
       </c>
     </row>
     <row r="135" spans="1:2" ht="17.25">
-      <c r="A135" s="10" t="s">
+      <c r="A135" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="B135" s="19">
+      <c r="B135" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:2" ht="17.25">
-      <c r="A136" s="10" t="s">
+      <c r="A136" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="B136" s="19">
+      <c r="B136" s="15">
         <v>15000</v>
       </c>
     </row>
     <row r="137" spans="1:2" ht="17.25">
-      <c r="A137" s="10" t="s">
+      <c r="A137" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="B137" s="19">
+      <c r="B137" s="15">
         <v>5000</v>
       </c>
     </row>
     <row r="138" spans="1:2" ht="17.25">
-      <c r="A138" s="10" t="s">
+      <c r="A138" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="B138" s="19">
+      <c r="B138" s="15">
         <v>15000</v>
       </c>
     </row>
     <row r="139" spans="1:2" ht="17.25">
-      <c r="A139" s="10" t="s">
+      <c r="A139" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="B139" s="19">
+      <c r="B139" s="15">
         <v>15000</v>
       </c>
     </row>
     <row r="140" spans="1:2" ht="16.5">
-      <c r="A140" s="9" t="s">
+      <c r="A140" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B140" s="9" t="s">
+      <c r="B140" s="5" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="141" spans="1:2" ht="17.25">
-      <c r="A141" s="10" t="s">
+      <c r="A141" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="B141" s="19">
+      <c r="B141" s="15">
         <v>6379</v>
       </c>
     </row>
     <row r="142" spans="1:2" ht="17.25">
-      <c r="A142" s="10" t="s">
+      <c r="A142" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="B142" s="19" t="b">
+      <c r="B142" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:2" ht="17.25">
-      <c r="A143" s="10" t="s">
+      <c r="A143" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="B143" s="19" t="s">
+      <c r="B143" s="15" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="144" spans="1:2" ht="17.25">
-      <c r="A144" s="10" t="s">
+      <c r="A144" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="B144" s="19" t="s">
+      <c r="B144" s="15" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="145" spans="1:2" ht="17.25">
-      <c r="A145" s="10" t="s">
+      <c r="A145" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="B145" s="19" t="s">
+      <c r="B145" s="15" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="146" spans="1:2" ht="17.25">
-      <c r="A146" s="10" t="s">
+      <c r="A146" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="B146" s="19" t="b">
+      <c r="B146" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:2" ht="16.5">
-      <c r="A147" s="9" t="s">
+      <c r="A147" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B147" s="9" t="s">
+      <c r="B147" s="5" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="148" spans="1:2" ht="17.25">
-      <c r="A148" s="10" t="s">
+      <c r="A148" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="B148" s="19">
+      <c r="B148" s="15">
         <v>5000</v>
       </c>
     </row>
     <row r="149" spans="1:2" ht="17.25">
-      <c r="A149" s="10" t="s">
+      <c r="A149" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="B149" s="19">
+      <c r="B149" s="15">
         <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:2" ht="17.25">
-      <c r="A150" s="10" t="s">
+      <c r="A150" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="B150" s="19">
+      <c r="B150" s="15">
         <v>200</v>
       </c>
     </row>
     <row r="151" spans="1:2" ht="17.25">
-      <c r="A151" s="10" t="s">
+      <c r="A151" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="B151" s="19">
+      <c r="B151" s="15">
         <v>5000</v>
       </c>
     </row>
     <row r="152" spans="1:2" ht="17.25">
-      <c r="A152" s="10" t="s">
+      <c r="A152" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="B152" s="19" t="s">
+      <c r="B152" s="15" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="153" spans="1:2" ht="16.5">
-      <c r="A153" s="9" t="s">
+      <c r="A153" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="B153" s="9" t="s">
+      <c r="B153" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="16.5">
-      <c r="A154" s="9" t="s">
+      <c r="A154" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B154" s="9" t="s">
+      <c r="B154" s="5" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="155" spans="1:2" ht="16.5">
-      <c r="A155" s="9" t="s">
+      <c r="A155" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="B155" s="9" t="s">
+      <c r="B155" s="5" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="156" spans="1:2" ht="16.5">
-      <c r="A156" s="9" t="s">
+      <c r="A156" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="B156" s="9" t="s">
+      <c r="B156" s="5" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="157" spans="1:2" ht="17.25">
-      <c r="A157" s="10" t="s">
+      <c r="A157" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="B157" s="19">
+      <c r="B157" s="15">
         <v>15</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="17.25">
-      <c r="A158" s="10" t="s">
+      <c r="A158" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="B158" s="19">
+      <c r="B158" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:2" ht="36">
-      <c r="A159" s="10" t="s">
+      <c r="A159" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="B159" s="19">
+      <c r="B159" s="15">
         <v>30000</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="17.25">
-      <c r="A160" s="10" t="s">
+      <c r="A160" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="B160" s="19">
+      <c r="B160" s="15">
         <v>600000</v>
       </c>
     </row>
     <row r="161" spans="1:2" ht="17.25">
-      <c r="A161" s="10" t="s">
+      <c r="A161" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="B161" s="19">
+      <c r="B161" s="15">
         <v>1800000</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="17.25">
-      <c r="A162" s="10" t="s">
+      <c r="A162" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="B162" s="15" t="s">
+      <c r="B162" s="11" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="17.25">
-      <c r="A163" s="10" t="s">
+      <c r="A163" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="B163" s="19" t="s">
+      <c r="B163" s="15" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="17.25">
-      <c r="A164" s="10" t="s">
+      <c r="A164" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="B164" s="15" t="s">
+      <c r="B164" s="11" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="33.75">
-      <c r="A165" s="10" t="s">
+      <c r="A165" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="B165" s="19" t="s">
+      <c r="B165" s="15" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="166" spans="1:2" ht="17.25">
-      <c r="A166" s="10" t="s">
+      <c r="A166" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="B166" s="19">
+      <c r="B166" s="15">
         <v>60</v>
       </c>
     </row>
     <row r="167" spans="1:2" ht="17.25">
-      <c r="A167" s="10" t="s">
+      <c r="A167" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="B167" s="19" t="s">
+      <c r="B167" s="15" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="168" spans="1:2" ht="36">
-      <c r="A168" s="10" t="s">
+      <c r="A168" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="B168" s="15" t="s">
+      <c r="B168" s="11" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="169" spans="1:2" ht="17.25">
-      <c r="A169" s="10" t="s">
+      <c r="A169" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="B169" s="19">
+      <c r="B169" s="15">
         <v>60</v>
       </c>
     </row>
     <row r="170" spans="1:2" ht="17.25">
-      <c r="A170" s="10" t="s">
+      <c r="A170" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="B170" s="19" t="s">
+      <c r="B170" s="15" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="171" spans="1:2" ht="17.25">
-      <c r="A171" s="10" t="s">
+      <c r="A171" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="B171" s="19" t="s">
+      <c r="B171" s="15" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="172" spans="1:2" ht="17.25">
-      <c r="A172" s="10" t="s">
+      <c r="A172" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="B172" s="19" t="s">
+      <c r="B172" s="15" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="173" spans="1:2" ht="17.25">
-      <c r="A173" s="10" t="s">
+      <c r="A173" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="B173" s="19" t="s">
+      <c r="B173" s="15" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="174" spans="1:2" ht="17.25">
-      <c r="A174" s="10" t="s">
+      <c r="A174" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="B174" s="19" t="b">
+      <c r="B174" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:2" ht="17.25">
-      <c r="A175" s="10" t="s">
+      <c r="A175" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="B175" s="19" t="b">
+      <c r="B175" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="17.25">
-      <c r="A176" s="10" t="s">
+      <c r="A176" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="B176" s="19" t="s">
+      <c r="B176" s="15" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="177" spans="1:2" ht="17.25">
-      <c r="A177" s="10" t="s">
+      <c r="A177" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="B177" s="19" t="s">
+      <c r="B177" s="15" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="178" spans="1:2" ht="17.25">
-      <c r="A178" s="10" t="s">
+      <c r="A178" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="B178" s="19" t="s">
+      <c r="B178" s="15" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="179" spans="1:2" ht="17.25">
-      <c r="A179" s="10" t="s">
+      <c r="A179" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="B179" s="19" t="s">
+      <c r="B179" s="15" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="180" spans="1:2" ht="36">
-      <c r="A180" s="10" t="s">
+      <c r="A180" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="B180" s="19">
+      <c r="B180" s="15">
         <v>4002</v>
       </c>
     </row>
     <row r="181" spans="1:2" ht="17.25">
-      <c r="A181" s="10" t="s">
+      <c r="A181" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="B181" s="19">
+      <c r="B181" s="15">
         <v>1106</v>
       </c>
     </row>
     <row r="182" spans="1:2" ht="17.25">
-      <c r="A182" s="10" t="s">
+      <c r="A182" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="B182" s="15" t="s">
+      <c r="B182" s="11" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="183" spans="1:2" ht="17.25">
-      <c r="A183" s="10" t="s">
+      <c r="A183" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="B183" s="19" t="s">
+      <c r="B183" s="15" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="184" spans="1:2" ht="33.75">
-      <c r="A184" s="10" t="s">
+      <c r="A184" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="B184" s="19" t="s">
+      <c r="B184" s="15" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="185" spans="1:2" ht="17.25">
-      <c r="A185" s="10" t="s">
+      <c r="A185" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="B185" s="19" t="s">
+      <c r="B185" s="15" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="186" spans="1:2" ht="17.25">
-      <c r="A186" s="10" t="s">
+      <c r="A186" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="B186" s="19" t="s">
+      <c r="B186" s="15" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="187" spans="1:2" ht="17.25">
-      <c r="A187" s="10" t="s">
+      <c r="A187" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="B187" s="19" t="s">
+      <c r="B187" s="15" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="188" spans="1:2" ht="17.25">
-      <c r="A188" s="10" t="s">
+      <c r="A188" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="B188" s="19">
+      <c r="B188" s="15">
         <v>30</v>
       </c>
     </row>
     <row r="189" spans="1:2" ht="17.25">
-      <c r="A189" s="10" t="s">
+      <c r="A189" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="B189" s="19" t="s">
+      <c r="B189" s="15" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="190" spans="1:2" ht="17.25">
-      <c r="A190" s="10" t="s">
+      <c r="A190" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="B190" s="19" t="s">
+      <c r="B190" s="15" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="191" spans="1:2" ht="17.25">
-      <c r="A191" s="10" t="s">
+      <c r="A191" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="B191" s="19" t="s">
+      <c r="B191" s="15" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="192" spans="1:2" ht="409.6">
-      <c r="A192" s="10" t="s">
+      <c r="A192" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B192" s="19" t="s">
+      <c r="B192" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="193" spans="1:2" ht="17.25">
-      <c r="A193" s="10" t="s">
+      <c r="A193" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="B193" s="15" t="s">
+      <c r="B193" s="11" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="194" spans="1:2" ht="17.25">
-      <c r="A194" s="10" t="s">
+      <c r="A194" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="B194" s="19" t="s">
+      <c r="B194" s="15" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="195" spans="1:2" ht="17.25">
-      <c r="A195" s="10" t="s">
+      <c r="A195" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="B195" s="19" t="s">
+      <c r="B195" s="15" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="196" spans="1:2" ht="121.5">
-      <c r="A196" s="11" t="s">
+      <c r="A196" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="B196" s="24" t="s">
+      <c r="B196" s="20" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="197" spans="1:2" ht="409.6">
-      <c r="A197" s="11" t="s">
+      <c r="A197" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="B197" s="24" t="s">
+      <c r="B197" s="20" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="198" spans="1:2" ht="17.25">
-      <c r="A198" s="10" t="s">
+      <c r="A198" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="B198" s="19" t="s">
+      <c r="B198" s="15" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="199" spans="1:2" ht="17.25">
-      <c r="A199" s="10" t="s">
+      <c r="A199" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="B199" s="19" t="s">
+      <c r="B199" s="15" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="200" spans="1:2" ht="17.25">
-      <c r="A200" s="10" t="s">
+      <c r="A200" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="B200" s="19" t="s">
+      <c r="B200" s="15" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="201" spans="1:2" ht="16.5">
-      <c r="A201" s="11" t="s">
+      <c r="A201" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="B201" s="19">
+      <c r="B201" s="15">
         <v>3</v>
       </c>
     </row>
     <row r="202" spans="1:2" ht="16.5">
-      <c r="A202" s="11" t="s">
+      <c r="A202" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="B202" s="19">
+      <c r="B202" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:2" ht="16.5">
-      <c r="A203" s="11" t="s">
+      <c r="A203" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="B203" s="19">
+      <c r="B203" s="15">
         <v>3</v>
       </c>
     </row>
     <row r="204" spans="1:2" ht="16.5">
-      <c r="A204" s="11" t="s">
+      <c r="A204" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="B204" s="19">
+      <c r="B204" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="205" spans="1:2" ht="16.5">
-      <c r="A205" s="11" t="s">
+      <c r="A205" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="B205" s="19" t="s">
+      <c r="B205" s="15" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="206" spans="1:2" ht="16.5">
-      <c r="A206" s="11" t="s">
+      <c r="A206" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="B206" s="19">
+      <c r="B206" s="15">
         <v>10</v>
       </c>
     </row>
     <row r="207" spans="1:2" ht="16.5">
-      <c r="A207" s="11" t="s">
+      <c r="A207" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="B207" s="19">
+      <c r="B207" s="15">
         <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:2" ht="16.5">
-      <c r="A208" s="11" t="s">
+      <c r="A208" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="B208" s="19">
+      <c r="B208" s="15">
         <v>24</v>
       </c>
     </row>
     <row r="209" spans="1:2" ht="16.5">
-      <c r="A209" s="11" t="s">
+      <c r="A209" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="B209" s="19">
+      <c r="B209" s="15">
         <v>200</v>
       </c>
     </row>
     <row r="210" spans="1:2" ht="16.5">
-      <c r="A210" s="11" t="s">
+      <c r="A210" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="B210" s="19">
+      <c r="B210" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:2" ht="16.5">
-      <c r="A211" s="11" t="s">
+      <c r="A211" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="B211" s="19">
+      <c r="B211" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="212" spans="1:2" ht="16.5">
-      <c r="A212" s="11" t="s">
+      <c r="A212" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="B212" s="19">
+      <c r="B212" s="15">
         <v>10</v>
       </c>
     </row>
     <row r="213" spans="1:2" ht="16.5">
-      <c r="A213" s="11" t="s">
+      <c r="A213" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="B213" s="19" t="b">
+      <c r="B213" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:2" ht="14.25">
-      <c r="A214" s="11"/>
-      <c r="B214" s="19"/>
+      <c r="A214" s="7"/>
+      <c r="B214" s="15"/>
     </row>
     <row r="215" spans="1:2" ht="17.25">
-      <c r="A215" s="10" t="s">
+      <c r="A215" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="B215" s="19" t="s">
+      <c r="B215" s="15" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="216" spans="1:2" ht="17.25">
-      <c r="A216" s="10" t="s">
+      <c r="A216" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="B216" s="19" t="s">
+      <c r="B216" s="15" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="217" spans="1:2" ht="17.25">
-      <c r="A217" s="10" t="s">
+      <c r="A217" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="B217" s="19" t="s">
+      <c r="B217" s="15" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="218" spans="1:2" ht="17.25">
-      <c r="A218" s="10" t="s">
+      <c r="A218" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="B218" s="19" t="s">
+      <c r="B218" s="15" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="219" spans="1:2" ht="17.25">
-      <c r="A219" s="10" t="s">
+      <c r="A219" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="B219" s="19" t="s">
+      <c r="B219" s="15" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="220" spans="1:2" ht="17.25">
-      <c r="A220" s="10" t="s">
+      <c r="A220" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="B220" s="19" t="s">
+      <c r="B220" s="15" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="221" spans="1:2" ht="17.25">
-      <c r="A221" s="10" t="s">
+      <c r="A221" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="B221" s="19" t="s">
+      <c r="B221" s="15" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="222" spans="1:2" ht="36">
-      <c r="A222" s="10" t="s">
+      <c r="A222" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="B222" s="19">
+      <c r="B222" s="15">
         <v>8400</v>
       </c>
     </row>
     <row r="223" spans="1:2" ht="17.25">
-      <c r="A223" s="10" t="s">
+      <c r="A223" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="B223" s="15" t="s">
+      <c r="B223" s="11" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="224" spans="1:2" ht="17.25">
-      <c r="A224" s="10" t="s">
+      <c r="A224" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="B224" s="19" t="s">
+      <c r="B224" s="15" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="225" spans="1:2" ht="17.25">
-      <c r="A225" s="10" t="s">
+      <c r="A225" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="B225" s="19" t="s">
+      <c r="B225" s="15" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="226" spans="1:2" ht="17.25">
-      <c r="A226" s="10" t="s">
+      <c r="A226" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="B226" s="19" t="s">
+      <c r="B226" s="15" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="227" spans="1:2" ht="17.25">
-      <c r="A227" s="10" t="s">
+      <c r="A227" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="B227" s="19" t="s">
+      <c r="B227" s="15" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="228" spans="1:2" ht="17.25">
-      <c r="A228" s="10" t="s">
+      <c r="A228" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="B228" s="19" t="s">
+      <c r="B228" s="15" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="229" spans="1:2" ht="17.25">
-      <c r="A229" s="10" t="s">
+      <c r="A229" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="B229" s="19" t="s">
+      <c r="B229" s="15" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="230" spans="1:2" ht="17.25">
-      <c r="A230" s="10" t="s">
+      <c r="A230" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="B230" s="19" t="s">
+      <c r="B230" s="15" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="231" spans="1:2" ht="17.25">
-      <c r="A231" s="10" t="s">
+      <c r="A231" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="B231" s="19" t="s">
+      <c r="B231" s="15" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="232" spans="1:2" ht="17.25">
-      <c r="A232" s="10" t="s">
+      <c r="A232" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="B232" s="19" t="s">
+      <c r="B232" s="15" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="233" spans="1:2" ht="17.25">
-      <c r="A233" s="10" t="s">
+      <c r="A233" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="B233" s="19">
+      <c r="B233" s="15">
         <v>60</v>
       </c>
     </row>
     <row r="234" spans="1:2" ht="17.25">
-      <c r="A234" s="10" t="s">
+      <c r="A234" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="B234" s="19" t="s">
+      <c r="B234" s="15" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="235" spans="1:2" ht="17.25">
-      <c r="A235" s="10" t="s">
+      <c r="A235" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="B235" s="19" t="s">
+      <c r="B235" s="15" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="236" spans="1:2" ht="17.25">
-      <c r="A236" s="10" t="s">
+      <c r="A236" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="B236" s="19" t="s">
+      <c r="B236" s="15" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="237" spans="1:2" ht="17.25">
-      <c r="A237" s="10" t="s">
+      <c r="A237" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="B237" s="19">
+      <c r="B237" s="15">
         <v>20</v>
       </c>
     </row>
     <row r="238" spans="1:2" ht="17.25">
-      <c r="A238" s="10" t="s">
+      <c r="A238" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="B238" s="15" t="s">
+      <c r="B238" s="11" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="239" spans="1:2" ht="17.25">
-      <c r="A239" s="10" t="s">
+      <c r="A239" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="B239" s="19" t="s">
+      <c r="B239" s="15" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="240" spans="1:2" ht="17.25">
-      <c r="A240" s="10" t="s">
+      <c r="A240" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="B240" s="15" t="s">
+      <c r="B240" s="11" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="241" spans="1:2" ht="17.25">
-      <c r="A241" s="10" t="s">
+      <c r="A241" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="B241" s="19" t="s">
+      <c r="B241" s="15" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="242" spans="1:2" ht="17.25">
-      <c r="A242" s="10" t="s">
+      <c r="A242" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="B242" s="19" t="s">
+      <c r="B242" s="15" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="243" spans="1:2" ht="16.5">
-      <c r="A243" s="9" t="s">
+      <c r="A243" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="B243" s="9" t="s">
+      <c r="B243" s="5" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="244" spans="1:2" ht="16.5">
-      <c r="A244" s="9" t="s">
+      <c r="A244" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="B244" s="9" t="s">
+      <c r="B244" s="5" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="245" spans="1:2" ht="17.25">
-      <c r="A245" s="10" t="s">
+      <c r="A245" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="B245" s="19" t="s">
+      <c r="B245" s="15" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="246" spans="1:2" ht="17.25">
-      <c r="A246" s="10" t="s">
+      <c r="A246" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="B246" s="19" t="s">
+      <c r="B246" s="15" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="247" spans="1:2" ht="17.25">
-      <c r="A247" s="10" t="s">
+      <c r="A247" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="B247" s="19">
+      <c r="B247" s="15">
         <v>60</v>
       </c>
     </row>
     <row r="248" spans="1:2" ht="17.25">
-      <c r="A248" s="10" t="s">
+      <c r="A248" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="B248" s="19" t="b">
+      <c r="B248" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:2" ht="16.5">
-      <c r="A249" s="9" t="s">
+      <c r="A249" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="B249" s="9" t="s">
+      <c r="B249" s="5" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="250" spans="1:2" ht="16.5">
-      <c r="A250" s="9" t="s">
+      <c r="A250" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="B250" s="9" t="s">
+      <c r="B250" s="5" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="251" spans="1:2" ht="16.5">
-      <c r="A251" s="9" t="s">
+      <c r="A251" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="B251" s="9" t="s">
+      <c r="B251" s="5" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="252" spans="1:2" ht="16.5">
-      <c r="A252" s="9" t="s">
+      <c r="A252" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="B252" s="9" t="s">
+      <c r="B252" s="5" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="253" spans="1:2" ht="16.5">
-      <c r="A253" s="9" t="s">
+      <c r="A253" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="B253" s="9" t="s">
+      <c r="B253" s="5" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="254" spans="1:2" ht="16.5">
-      <c r="A254" s="9" t="s">
+      <c r="A254" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="B254" s="9" t="s">
+      <c r="B254" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="255" spans="1:2" ht="16.5">
-      <c r="A255" s="9" t="s">
+      <c r="A255" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="B255" s="9" t="s">
+      <c r="B255" s="5" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="256" spans="1:2" ht="16.5">
-      <c r="A256" s="9" t="s">
+      <c r="A256" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="B256" s="9" t="s">
+      <c r="B256" s="5" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="257" spans="1:2" ht="16.5">
-      <c r="A257" s="9" t="s">
+      <c r="A257" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="B257" s="25" t="s">
+      <c r="B257" s="21" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="258" spans="1:2" ht="16.5">
-      <c r="A258" s="9" t="s">
+      <c r="A258" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="B258" s="26" t="s">
+      <c r="B258" s="22" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="259" spans="1:2" ht="16.5">
-      <c r="A259" s="9" t="s">
+      <c r="A259" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B259" s="26" t="s">
+      <c r="B259" s="22" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="260" spans="1:2" ht="16.5">
-      <c r="A260" s="9" t="s">
+      <c r="A260" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="B260" s="26">
+      <c r="B260" s="22">
         <v>1414</v>
       </c>
     </row>
     <row r="261" spans="1:2" ht="16.5">
-      <c r="A261" s="9" t="s">
+      <c r="A261" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="B261" s="26" t="s">
+      <c r="B261" s="22" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="262" spans="1:2" ht="16.5">
-      <c r="A262" s="9" t="s">
+      <c r="A262" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B262" s="26" t="s">
+      <c r="B262" s="22" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="263" spans="1:2" ht="16.5">
-      <c r="A263" s="9" t="s">
+      <c r="A263" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="B263" s="27" t="s">
+      <c r="B263" s="23" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="264" spans="1:2" ht="17.25">
-      <c r="A264" s="10" t="s">
+      <c r="A264" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="B264" s="19" t="s">
+      <c r="B264" s="15" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="265" spans="1:2" ht="16.5">
-      <c r="A265" s="9" t="s">
+      <c r="A265" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="B265" s="26" t="s">
+      <c r="B265" s="22" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="266" spans="1:2" ht="16.5">
-      <c r="A266" s="9" t="s">
+      <c r="A266" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="B266" s="26">
+      <c r="B266" s="22">
         <v>1414</v>
       </c>
     </row>
     <row r="267" spans="1:2" ht="16.5">
-      <c r="A267" s="9" t="s">
+      <c r="A267" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="B267" s="26" t="s">
+      <c r="B267" s="22" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="268" spans="1:2" ht="16.5">
-      <c r="A268" s="9" t="s">
+      <c r="A268" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="B268" s="26" t="s">
+      <c r="B268" s="22" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="269" spans="1:2" ht="16.5">
-      <c r="A269" s="9" t="s">
+      <c r="A269" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="B269" s="26" t="s">
+      <c r="B269" s="22" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="270" spans="1:2" ht="16.5">
-      <c r="A270" s="9" t="s">
+      <c r="A270" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="B270" s="26" t="s">
+      <c r="B270" s="22" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="271" spans="1:2" ht="16.5">
-      <c r="A271" s="9" t="s">
+      <c r="A271" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="B271" s="26" t="s">
+      <c r="B271" s="22" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="272" spans="1:2" ht="16.5">
-      <c r="A272" s="11" t="s">
+      <c r="A272" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="B272" s="19"/>
+      <c r="B272" s="15"/>
     </row>
     <row r="273" spans="1:2" ht="16.5">
-      <c r="A273" s="11" t="s">
+      <c r="A273" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="B273" s="19">
+      <c r="B273" s="15">
         <v>3</v>
       </c>
     </row>
     <row r="274" spans="1:2" ht="16.5">
-      <c r="A274" s="11" t="s">
+      <c r="A274" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="B274" s="19">
+      <c r="B274" s="15">
         <v>500</v>
       </c>
     </row>
     <row r="275" spans="1:2" ht="16.5">
-      <c r="A275" s="11" t="s">
+      <c r="A275" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="B275" s="19">
+      <c r="B275" s="15">
         <v>50</v>
       </c>
     </row>
     <row r="276" spans="1:2" ht="16.5">
-      <c r="A276" s="11" t="s">
+      <c r="A276" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="B276" s="19">
+      <c r="B276" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:2" ht="16.5">
-      <c r="A277" s="11" t="s">
+      <c r="A277" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="B277" s="19">
+      <c r="B277" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:2" ht="16.5">
-      <c r="A278" s="11" t="s">
+      <c r="A278" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="B278" s="19">
+      <c r="B278" s="15">
         <v>30</v>
       </c>
     </row>
     <row r="279" spans="1:2" ht="16.5">
-      <c r="A279" s="11" t="s">
+      <c r="A279" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="B279" s="19"/>
+      <c r="B279" s="15"/>
     </row>
     <row r="280" spans="1:2" ht="16.5">
-      <c r="A280" s="11" t="s">
+      <c r="A280" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="B280" s="19" t="s">
+      <c r="B280" s="15" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="281" spans="1:2" ht="16.5">
-      <c r="A281" s="11" t="s">
+      <c r="A281" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="B281" s="19" t="s">
+      <c r="B281" s="15" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="282" spans="1:2" ht="16.5">
-      <c r="A282" s="11" t="s">
+      <c r="A282" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="B282" s="19" t="s">
+      <c r="B282" s="15" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="283" spans="1:2" ht="16.5">
-      <c r="A283" s="11" t="s">
+      <c r="A283" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="B283" s="19" t="s">
+      <c r="B283" s="15" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="284" spans="1:2" ht="16.5">
-      <c r="A284" s="11" t="s">
+      <c r="A284" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="B284" s="19" t="s">
+      <c r="B284" s="15" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="285" spans="1:2" ht="16.5">
-      <c r="A285" s="11" t="s">
+      <c r="A285" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="B285" s="19" t="s">
+      <c r="B285" s="15" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="286" spans="1:2" ht="16.5">
-      <c r="A286" s="11" t="s">
+      <c r="A286" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="B286" s="19" t="s">
+      <c r="B286" s="15" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="287" spans="1:2" ht="16.5">
-      <c r="A287" s="11" t="s">
+      <c r="A287" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="B287" s="19">
+      <c r="B287" s="15">
         <v>30</v>
       </c>
     </row>
     <row r="288" spans="1:2" ht="16.5">
-      <c r="A288" s="11" t="s">
+      <c r="A288" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="B288" s="19" t="s">
+      <c r="B288" s="15" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="289" spans="1:2" ht="16.5">
-      <c r="A289" s="11" t="s">
+      <c r="A289" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="B289" s="19">
+      <c r="B289" s="15">
         <v>5000</v>
       </c>
     </row>
     <row r="290" spans="1:2" ht="16.5">
-      <c r="A290" s="11" t="s">
+      <c r="A290" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="B290" s="19">
+      <c r="B290" s="15">
         <v>10000</v>
       </c>
     </row>
     <row r="291" spans="1:2" ht="16.5">
-      <c r="A291" s="11" t="s">
+      <c r="A291" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="B291" s="19">
+      <c r="B291" s="15">
         <v>10000</v>
       </c>
     </row>
     <row r="292" spans="1:2" ht="16.5">
-      <c r="A292" s="11" t="s">
+      <c r="A292" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="B292" s="19">
+      <c r="B292" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="293" spans="1:2" ht="16.5">
-      <c r="A293" s="11" t="s">
+      <c r="A293" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="B293" s="19">
+      <c r="B293" s="15">
         <v>300</v>
       </c>
     </row>
     <row r="294" spans="1:2" ht="16.5">
-      <c r="A294" s="11" t="s">
+      <c r="A294" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="B294" s="19">
+      <c r="B294" s="15">
         <v>0.3</v>
       </c>
     </row>
     <row r="295" spans="1:2" ht="16.5">
-      <c r="A295" s="11" t="s">
+      <c r="A295" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="B295" s="19">
+      <c r="B295" s="15">
         <v>16</v>
       </c>
     </row>
     <row r="296" spans="1:2" ht="16.5">
-      <c r="A296" s="11" t="s">
+      <c r="A296" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="B296" s="19">
+      <c r="B296" s="15">
         <v>40</v>
       </c>
     </row>
     <row r="297" spans="1:2" ht="16.5">
-      <c r="A297" s="11" t="s">
+      <c r="A297" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="B297" s="19">
+      <c r="B297" s="15">
         <v>100</v>
       </c>
     </row>
     <row r="298" spans="1:2" ht="16.5">
-      <c r="A298" s="11" t="s">
+      <c r="A298" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="B298" s="19">
+      <c r="B298" s="15">
         <v>30</v>
       </c>
     </row>
     <row r="299" spans="1:2" ht="16.5">
-      <c r="A299" s="11" t="s">
+      <c r="A299" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="B299" s="19">
+      <c r="B299" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="300" spans="1:2" ht="16.5">
-      <c r="A300" s="11" t="s">
+      <c r="A300" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="B300" s="19">
+      <c r="B300" s="15">
         <v>500</v>
       </c>
     </row>
     <row r="301" spans="1:2" ht="16.5">
-      <c r="A301" s="11" t="s">
+      <c r="A301" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="B301" s="19">
+      <c r="B301" s="15">
         <v>500</v>
       </c>
     </row>
     <row r="302" spans="1:2" ht="16.5">
-      <c r="A302" s="11" t="s">
+      <c r="A302" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="B302" s="19">
+      <c r="B302" s="15">
         <v>4</v>
       </c>
     </row>
     <row r="303" spans="1:2" ht="16.5">
-      <c r="A303" s="11" t="s">
+      <c r="A303" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="B303" s="19">
+      <c r="B303" s="15">
         <v>4</v>
       </c>
     </row>
     <row r="304" spans="1:2" ht="33.75">
-      <c r="A304" s="11" t="s">
+      <c r="A304" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="B304" s="19" t="s">
+      <c r="B304" s="15" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="305" spans="1:2" ht="16.5">
-      <c r="A305" s="11" t="s">
+      <c r="A305" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="B305" s="19" t="s">
+      <c r="B305" s="15" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="306" spans="1:2" ht="16.5">
-      <c r="A306" s="11" t="s">
+      <c r="A306" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="B306" s="19">
+      <c r="B306" s="15">
         <v>20</v>
       </c>
     </row>
     <row r="307" spans="1:2" ht="16.5">
-      <c r="A307" s="11" t="s">
+      <c r="A307" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="B307" s="19">
+      <c r="B307" s="15">
         <v>60</v>
       </c>
     </row>
     <row r="308" spans="1:2" ht="16.5">
-      <c r="A308" s="11" t="s">
+      <c r="A308" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="B308" s="19" t="b">
+      <c r="B308" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="309" spans="1:2" ht="16.5">
-      <c r="A309" s="11" t="s">
+      <c r="A309" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="B309" s="19">
+      <c r="B309" s="15">
         <v>60000</v>
       </c>
     </row>
     <row r="310" spans="1:2" ht="16.5">
-      <c r="A310" s="9" t="s">
+      <c r="A310" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="B310" s="21"/>
+      <c r="B310" s="17"/>
     </row>
     <row r="311" spans="1:2" ht="16.5">
-      <c r="A311" s="11" t="s">
+      <c r="A311" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="B311" s="11" t="s">
+      <c r="B311" s="7" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="312" spans="1:2" ht="16.5">
-      <c r="A312" s="11" t="s">
+      <c r="A312" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="B312" s="11" t="s">
+      <c r="B312" s="7" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="313" spans="1:2" ht="16.5">
-      <c r="A313" s="9" t="s">
+      <c r="A313" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="B313" s="21"/>
+      <c r="B313" s="17"/>
     </row>
     <row r="314" spans="1:2" ht="16.5">
-      <c r="A314" s="9" t="s">
+      <c r="A314" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="B314" s="21"/>
+      <c r="B314" s="17"/>
     </row>
     <row r="315" spans="1:2" ht="14.25"/>
     <row r="316" spans="1:2" ht="14.25"/>
@@ -4510,50 +4477,50 @@
     <row r="321" ht="14.25"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B8" r:id="rId1" xr:uid="{EFFB9478-F3D3-44F3-968D-F18BB829929D}"/>
-    <hyperlink ref="B10" r:id="rId2" xr:uid="{6494778D-BEE6-49BA-830E-A426F04490F5}"/>
-    <hyperlink ref="B7" r:id="rId3" xr:uid="{C33A896D-6AAB-43F1-8209-0A9B42E6FF61}"/>
-    <hyperlink ref="B14" r:id="rId4" xr:uid="{E70A91CA-33A7-43E1-BC8B-54B242D3CFF8}"/>
-    <hyperlink ref="B20" r:id="rId5" xr:uid="{A4DB795C-5D43-4EE4-A7B9-DB4F73C249A4}"/>
-    <hyperlink ref="B23" r:id="rId6" xr:uid="{A62E78B7-6CB3-4A98-89CD-182D35E3ABC0}"/>
-    <hyperlink ref="B24" r:id="rId7" xr:uid="{839A7C92-3DC9-47FA-ABE1-C6374C024830}"/>
-    <hyperlink ref="B26" r:id="rId8" xr:uid="{2347C1C9-DA87-4BE9-AB1B-F96160156477}"/>
-    <hyperlink ref="B32" r:id="rId9" xr:uid="{1EE94353-D655-4720-9BFA-ADD35B8FD0D1}"/>
-    <hyperlink ref="B33" r:id="rId10" xr:uid="{961F6A1B-5FCC-4366-8BF9-6143F1AE7B9C}"/>
-    <hyperlink ref="B34" r:id="rId11" xr:uid="{F35D92A0-91D9-41F5-8D60-2ADF1AFC325E}"/>
-    <hyperlink ref="B35" r:id="rId12" xr:uid="{BA271DEF-1C74-4A51-9B8E-F41DA575C830}"/>
-    <hyperlink ref="B37" r:id="rId13" xr:uid="{35CC327D-CC46-4F6A-B9ED-0732B4627FB4}"/>
-    <hyperlink ref="B39" r:id="rId14" xr:uid="{95CFEA8B-123D-4A63-9062-EA93D6E065E5}"/>
-    <hyperlink ref="B40" r:id="rId15" xr:uid="{6A9478CF-769D-4D0F-A250-BC920C25E145}"/>
-    <hyperlink ref="B41" r:id="rId16" xr:uid="{4AA4D758-13B9-473D-AF58-34C822D014EB}"/>
-    <hyperlink ref="B42" r:id="rId17" xr:uid="{013FB608-1FC4-4BC8-92C7-444189F01942}"/>
-    <hyperlink ref="B45" r:id="rId18" xr:uid="{26C347CE-4DEB-48A1-8713-15EFA400EF0D}"/>
-    <hyperlink ref="B46" r:id="rId19" xr:uid="{D8A42CBC-4209-41E9-970A-8C000D7EEB7C}"/>
-    <hyperlink ref="B47" r:id="rId20" xr:uid="{C7CBC0FE-F9EF-458D-B628-EE0239DB0CC5}"/>
-    <hyperlink ref="B48" r:id="rId21" xr:uid="{135840C9-2A5B-46FE-8BAA-70173E2D5F05}"/>
-    <hyperlink ref="B49" r:id="rId22" xr:uid="{A38F7D76-3940-45F3-8D52-A47FCC5A4021}"/>
-    <hyperlink ref="B57" r:id="rId23" xr:uid="{8B051ADC-7F69-419A-9546-1359C77DB41B}"/>
-    <hyperlink ref="B58" r:id="rId24" xr:uid="{181F989E-1D96-4375-91C1-03DCC7F63D93}"/>
-    <hyperlink ref="B61" r:id="rId25" xr:uid="{56C7EE91-F333-460D-B058-9EA12E067730}"/>
-    <hyperlink ref="B67" r:id="rId26" xr:uid="{C54869B4-05CF-4EAB-AC81-03368FA6E8CB}"/>
-    <hyperlink ref="B68" r:id="rId27" xr:uid="{092B9D63-D7C9-4C5B-A06E-DC8F9CFC074C}"/>
-    <hyperlink ref="B87" r:id="rId28" xr:uid="{E868728E-701E-4E5D-B2F5-9B6EA1D20305}"/>
-    <hyperlink ref="B91" r:id="rId29" xr:uid="{B5FD6EE7-8608-428D-AB68-34656F28137B}"/>
-    <hyperlink ref="B92" r:id="rId30" xr:uid="{6CDBF3FA-E4A3-4345-8663-F69219F51ED2}"/>
-    <hyperlink ref="B99" r:id="rId31" xr:uid="{629B018B-B146-4855-92D1-80404C226B61}"/>
-    <hyperlink ref="B116" r:id="rId32" xr:uid="{654078BD-9FCC-4D7F-B682-709C27CD5204}"/>
-    <hyperlink ref="B120" r:id="rId33" xr:uid="{2B37563E-C349-4FD7-A65D-BD39E05D1140}"/>
-    <hyperlink ref="B122" r:id="rId34" xr:uid="{C36671F9-E150-4775-B2AA-DDF68E0FB18F}"/>
-    <hyperlink ref="B126" r:id="rId35" xr:uid="{B3F5A6E6-D8F2-4CCF-958E-58768D75561A}"/>
-    <hyperlink ref="B129" r:id="rId36" xr:uid="{86AE796F-5F30-4B2D-8A12-32F50AA0D507}"/>
-    <hyperlink ref="B162" r:id="rId37" xr:uid="{AC3DEE98-C258-4DB8-95DA-7FF78128607D}"/>
-    <hyperlink ref="B164" r:id="rId38" xr:uid="{88089A43-BB2E-4668-8428-5240BE151CFA}"/>
-    <hyperlink ref="B168" r:id="rId39" xr:uid="{01CDDEF7-2416-4176-B071-47E3B19754C2}"/>
-    <hyperlink ref="B182" r:id="rId40" xr:uid="{6DE135C5-3B4B-4093-B267-EF8DDDEB7655}"/>
-    <hyperlink ref="B193" r:id="rId41" xr:uid="{9C58B127-0F28-4F10-BD54-4A834F83FAE6}"/>
-    <hyperlink ref="B223" r:id="rId42" xr:uid="{BC4C185B-79D0-46F0-A293-85B48ABAF328}"/>
-    <hyperlink ref="B238" r:id="rId43" xr:uid="{7EBF6DE5-99E7-4890-B05A-D87E1F6CFFB8}"/>
-    <hyperlink ref="B240" r:id="rId44" xr:uid="{ABFC02F0-D7B9-463B-82F7-05ACBFB2476D}"/>
+    <hyperlink ref="B8" r:id="rId1" xr:uid="{435FAF1F-1E44-41D2-9046-BD42342C6769}"/>
+    <hyperlink ref="B10" r:id="rId2" xr:uid="{4804C597-5B5A-473D-BB9F-D21E5EC0AC41}"/>
+    <hyperlink ref="B7" r:id="rId3" xr:uid="{F98D2623-52A5-466F-B4F2-6F76D7D84592}"/>
+    <hyperlink ref="B14" r:id="rId4" xr:uid="{5F8B2F01-C2F6-4AF5-A04F-E5888F1A524C}"/>
+    <hyperlink ref="B20" r:id="rId5" xr:uid="{444CF7BA-D835-42B0-9022-8E063441C816}"/>
+    <hyperlink ref="B23" r:id="rId6" xr:uid="{7A0BE37E-3BA2-4619-B934-2A7ADFA2898C}"/>
+    <hyperlink ref="B24" r:id="rId7" xr:uid="{C30D2680-88A7-4975-B94A-266335607E55}"/>
+    <hyperlink ref="B26" r:id="rId8" xr:uid="{D12AD80E-E9BE-46C6-8ED3-158E36028C95}"/>
+    <hyperlink ref="B32" r:id="rId9" xr:uid="{36B1D581-A195-4BA8-AA12-EC7317D2E39B}"/>
+    <hyperlink ref="B33" r:id="rId10" xr:uid="{FB399217-4A51-48D3-81D4-6F14577C9C89}"/>
+    <hyperlink ref="B34" r:id="rId11" xr:uid="{5356D76E-8B22-4184-AD7A-B1E047816DAD}"/>
+    <hyperlink ref="B35" r:id="rId12" xr:uid="{59F2E134-6AE9-4DE7-80BC-7ADC414F304F}"/>
+    <hyperlink ref="B37" r:id="rId13" xr:uid="{BE30ABD6-3EDB-4556-8380-16249E7425BA}"/>
+    <hyperlink ref="B39" r:id="rId14" xr:uid="{793092E2-60FD-4907-928B-CD669C9F4BAB}"/>
+    <hyperlink ref="B40" r:id="rId15" xr:uid="{9C589059-2D50-45CD-BA2C-975DA85A2A37}"/>
+    <hyperlink ref="B41" r:id="rId16" xr:uid="{CA1E7FE6-D285-4AF3-B977-FAB625C59DFD}"/>
+    <hyperlink ref="B42" r:id="rId17" xr:uid="{E17CD5E5-EE39-4FBD-B19E-BC576B55CA75}"/>
+    <hyperlink ref="B45" r:id="rId18" xr:uid="{4FC16154-7E2A-48BC-9EA1-FF428DC8BE90}"/>
+    <hyperlink ref="B46" r:id="rId19" xr:uid="{2A0056BF-11D4-4346-AA1C-0864734F35A8}"/>
+    <hyperlink ref="B47" r:id="rId20" xr:uid="{1D52F802-8911-4133-AA5A-9638E1FB468C}"/>
+    <hyperlink ref="B48" r:id="rId21" xr:uid="{64AE3EC7-658B-4E4F-8D37-CCE0FCB10CC9}"/>
+    <hyperlink ref="B49" r:id="rId22" xr:uid="{DE039FCD-A70D-46D9-B149-1CD47E708266}"/>
+    <hyperlink ref="B57" r:id="rId23" xr:uid="{0766CA18-9F88-4370-8C8A-32EF01DDF79A}"/>
+    <hyperlink ref="B58" r:id="rId24" xr:uid="{BF9C636E-1EB3-41B2-A889-B24C5A96FF5C}"/>
+    <hyperlink ref="B61" r:id="rId25" xr:uid="{19AB1920-8F68-49A8-AAE1-2DA1D64DE9ED}"/>
+    <hyperlink ref="B67" r:id="rId26" xr:uid="{10D6280C-D7AE-4A05-8768-6D657ABF0CBD}"/>
+    <hyperlink ref="B68" r:id="rId27" xr:uid="{2E196C9A-C5C7-47E1-A4B0-DEDA32BACD47}"/>
+    <hyperlink ref="B87" r:id="rId28" xr:uid="{34E7B714-81BB-4729-BFA2-213D556DDCC8}"/>
+    <hyperlink ref="B91" r:id="rId29" xr:uid="{346A6100-3C3A-4DFC-A53C-CE377FFB627D}"/>
+    <hyperlink ref="B92" r:id="rId30" xr:uid="{264CC008-86A5-4F33-9EF6-27D0DB6D3E0C}"/>
+    <hyperlink ref="B99" r:id="rId31" xr:uid="{11BFCC4C-DA7B-4466-A5A6-663D4001BE6B}"/>
+    <hyperlink ref="B116" r:id="rId32" xr:uid="{5AA20908-FD1F-4692-B7CC-A4B9AA9D370B}"/>
+    <hyperlink ref="B120" r:id="rId33" xr:uid="{2E7A808D-2F6B-417D-A9E1-3177806E7BE0}"/>
+    <hyperlink ref="B122" r:id="rId34" xr:uid="{45D6B27C-A023-497B-8775-66891767DEEF}"/>
+    <hyperlink ref="B126" r:id="rId35" xr:uid="{440A9916-5E49-441E-836B-FB4BA694DA05}"/>
+    <hyperlink ref="B129" r:id="rId36" xr:uid="{695B11A0-66A3-464B-883C-DB92799E0561}"/>
+    <hyperlink ref="B162" r:id="rId37" xr:uid="{9014E8F3-35E1-4D06-8063-933C945B1573}"/>
+    <hyperlink ref="B164" r:id="rId38" xr:uid="{AD27556C-B69A-4CE2-9D0C-6620515DEEAE}"/>
+    <hyperlink ref="B168" r:id="rId39" xr:uid="{C93C0AAE-6EBE-4AA3-8D63-E31C1D3EAEA5}"/>
+    <hyperlink ref="B182" r:id="rId40" xr:uid="{E792551C-9B4E-4DE0-81FC-1702183BA973}"/>
+    <hyperlink ref="B193" r:id="rId41" xr:uid="{5DD6F146-7D81-48DD-9F67-DC4434885957}"/>
+    <hyperlink ref="B223" r:id="rId42" xr:uid="{DCFC9F14-B6FB-40BF-9921-F4BF440A368C}"/>
+    <hyperlink ref="B238" r:id="rId43" xr:uid="{1DC6D6DC-B1B7-4C99-BB8C-1F0F4D1BEBE9}"/>
+    <hyperlink ref="B240" r:id="rId44" xr:uid="{12405D19-EDFD-448F-8E59-56C43E4CF03C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -4564,7 +4531,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BA10D3F-9410-466B-8CA1-0A97526CEA81}">
-  <dimension ref="A1:B322"/>
+  <dimension ref="A1:B314"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="56.375" customWidth="1"/>
@@ -4572,2590 +4539,2526 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.5">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="16.5">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="10" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="16.5">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="16.5">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="10" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="16.5">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="10">
         <v>5432</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="16.5">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="17.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="14" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="17.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="14" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="16.5">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="12" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="17.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="16.5">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="17.25">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="20" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="17.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="20" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="17.25">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="20" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="17.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17.25">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="20"/>
+      <c r="B17" s="16"/>
     </row>
     <row r="18" spans="1:2" ht="17.25">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="20"/>
+      <c r="B18" s="16"/>
     </row>
     <row r="19" spans="1:2" ht="17.25">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="20"/>
+      <c r="B19" s="16"/>
     </row>
     <row r="20" spans="1:2" ht="17.25">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="17.25">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="19"/>
+      <c r="B21" s="15"/>
     </row>
     <row r="22" spans="1:2" ht="16.5">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="5" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="17.25">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="11" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="16.5">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="11" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="334.5">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="20" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="17.25">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="12" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15">
-      <c r="A27" s="10"/>
-      <c r="B27" s="19"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="15"/>
     </row>
     <row r="28" spans="1:2" ht="15">
-      <c r="A28" s="10"/>
-      <c r="B28" s="19"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="15"/>
     </row>
     <row r="29" spans="1:2" ht="17.25">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="19"/>
+      <c r="B29" s="15"/>
     </row>
     <row r="30" spans="1:2" ht="17.25">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="17.25">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="17.25">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="17.25">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="17.25">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="17.25">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="17.25">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B36" s="21"/>
+      <c r="B36" s="17"/>
     </row>
     <row r="37" spans="1:2" ht="17.25">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="11" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="17.25">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="15" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="17.25">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B39" s="18" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="17.25">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="11" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="17.25">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="11" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="17.25">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="11" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="17.25">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B43" s="19" t="s">
+      <c r="B43" s="15" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="17.25">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="15" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="17.25">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="11" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="17.25">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="17.25">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="17.25">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="B48" s="11" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="17.25">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B49" s="15" t="s">
+      <c r="B49" s="11" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="17.25">
-      <c r="A50" s="10" t="s">
+      <c r="A50" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="15" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="17.25">
-      <c r="A51" s="10" t="s">
+      <c r="A51" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B51" s="19" t="s">
+      <c r="B51" s="15" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="17.25">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B52" s="19">
+      <c r="B52" s="15">
         <v>3600</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="17.25">
-      <c r="A53" s="10" t="s">
+      <c r="A53" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B53" s="19">
+      <c r="B53" s="15">
         <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="17.25">
-      <c r="A54" s="10" t="s">
+      <c r="A54" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="15" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="17.25">
-      <c r="A55" s="10" t="s">
+      <c r="A55" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="19">
+      <c r="B55" s="15">
         <v>3600</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="17.25">
-      <c r="A56" s="10" t="s">
+      <c r="A56" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B56" s="19">
+      <c r="B56" s="15">
         <v>30</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="17.25">
-      <c r="A57" s="10" t="s">
+      <c r="A57" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B57" s="15" t="s">
+      <c r="B57" s="11" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="17.25">
-      <c r="A58" s="10" t="s">
+      <c r="A58" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="11" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="17.25">
-      <c r="A59" s="10" t="s">
+      <c r="A59" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B59" s="19">
+      <c r="B59" s="15">
         <v>3660</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="17.25">
-      <c r="A60" s="10" t="s">
+      <c r="A60" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B60" s="19" t="s">
+      <c r="B60" s="15" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="17.25">
-      <c r="A61" s="10" t="s">
+      <c r="A61" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B61" s="15" t="s">
+      <c r="B61" s="11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="17.25">
-      <c r="A62" s="10" t="s">
+      <c r="A62" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B62" s="19">
+      <c r="B62" s="15">
         <v>600</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="17.25">
-      <c r="A63" s="10" t="s">
+      <c r="A63" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B63" s="19">
+      <c r="B63" s="15">
         <v>60000</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="17.25">
-      <c r="A64" s="10" t="s">
+      <c r="A64" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B64" s="19">
+      <c r="B64" s="15">
         <v>60000</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="17.25">
-      <c r="A65" s="10" t="s">
+      <c r="A65" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B65" s="19">
+      <c r="B65" s="15">
         <v>3660</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="17.25">
-      <c r="A66" s="10" t="s">
+      <c r="A66" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B66" s="19">
+      <c r="B66" s="15">
         <v>3600</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="16.5">
-      <c r="A67" s="13" t="s">
+      <c r="A67" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B67" s="13" t="s">
+      <c r="B67" s="9" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="17.25">
-      <c r="A68" s="10" t="s">
+      <c r="A68" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="B68" s="15" t="s">
+      <c r="B68" s="11" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="17.25">
-      <c r="A69" s="10" t="s">
+      <c r="A69" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B69" s="19" t="s">
+      <c r="B69" s="15" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="17.25">
-      <c r="A70" s="10" t="s">
+      <c r="A70" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B70" s="19" t="s">
+      <c r="B70" s="15" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="17.25">
-      <c r="A71" s="10" t="s">
+      <c r="A71" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B71" s="19" t="s">
+      <c r="B71" s="15" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="17.25">
-      <c r="A72" s="10" t="s">
+      <c r="A72" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B72" s="19">
+      <c r="B72" s="15">
         <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="17.25">
-      <c r="A73" s="10" t="s">
+      <c r="A73" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B73" s="19" t="s">
+      <c r="B73" s="15" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="17.25">
-      <c r="A74" s="10" t="s">
+      <c r="A74" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B74" s="19" t="s">
+      <c r="B74" s="15" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="17.25">
-      <c r="A75" s="10" t="s">
+      <c r="A75" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B75" s="23" t="s">
+      <c r="B75" s="19" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="17.25">
-      <c r="A76" s="10" t="s">
+      <c r="A76" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B76" s="19" t="s">
+      <c r="B76" s="15" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="17.25">
-      <c r="A77" s="10" t="s">
+      <c r="A77" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B77" s="19">
+      <c r="B77" s="15">
         <v>10000</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="17.25">
-      <c r="A78" s="10" t="s">
+      <c r="A78" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B78" s="19" t="s">
+      <c r="B78" s="15" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="17.25">
-      <c r="A79" s="10" t="s">
+      <c r="A79" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="B79" s="19" t="s">
+      <c r="B79" s="15" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="17.25">
-      <c r="A80" s="10" t="s">
+      <c r="A80" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B80" s="19">
+      <c r="B80" s="15">
         <v>5000</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="17.25">
-      <c r="A81" s="10" t="s">
+      <c r="A81" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B81" s="19">
+      <c r="B81" s="15">
         <v>30</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="17.25">
-      <c r="A82" s="10" t="s">
+      <c r="A82" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B82" s="19" t="s">
+      <c r="B82" s="15" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="17.25">
-      <c r="A83" s="10" t="s">
+      <c r="A83" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B83" s="19">
+      <c r="B83" s="15">
         <v>8000</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="17.25">
-      <c r="A84" s="10" t="s">
+      <c r="A84" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B84" s="19" t="s">
+      <c r="B84" s="15" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="85" spans="1:2" ht="17.25">
-      <c r="A85" s="10" t="s">
+      <c r="A85" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B85" s="19">
+      <c r="B85" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:2" ht="17.25">
-      <c r="A86" s="10" t="s">
+      <c r="A86" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="B86" s="19" t="s">
+      <c r="B86" s="15" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="17.25">
-      <c r="A87" s="10" t="s">
+      <c r="A87" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B87" s="15" t="s">
+      <c r="B87" s="11" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="88" spans="1:2" ht="17.25">
-      <c r="A88" s="10" t="s">
+      <c r="A88" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B88" s="19">
+      <c r="B88" s="15">
         <v>262144</v>
       </c>
     </row>
     <row r="89" spans="1:2" ht="16.5">
-      <c r="A89" s="9" t="s">
+      <c r="A89" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B89" s="9" t="s">
+      <c r="B89" s="5" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="90" spans="1:2" ht="16.5">
-      <c r="A90" s="9" t="s">
+      <c r="A90" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B90" s="9" t="s">
+      <c r="B90" s="5" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="16.5">
-      <c r="A91" s="9" t="s">
+      <c r="A91" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B91" s="13" t="s">
+      <c r="B91" s="9" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="16.5">
-      <c r="A92" s="13" t="s">
+      <c r="A92" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B92" s="13" t="s">
+      <c r="B92" s="9" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="93" spans="1:2" ht="17.25">
-      <c r="A93" s="10" t="s">
+      <c r="A93" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B93" s="19" t="s">
+      <c r="B93" s="15" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="94" spans="1:2" ht="17.25">
-      <c r="A94" s="10" t="s">
+      <c r="A94" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="B94" s="19" t="s">
+      <c r="B94" s="15" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="17.25">
-      <c r="A95" s="10" t="s">
+      <c r="A95" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B95" s="19" t="s">
+      <c r="B95" s="15" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="17.25">
-      <c r="A96" s="10" t="s">
+      <c r="A96" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B96" s="19" t="s">
+      <c r="B96" s="15" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="17.25">
-      <c r="A97" s="10" t="s">
+      <c r="A97" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B97" s="19" t="s">
+      <c r="B97" s="15" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="98" spans="1:2" ht="17.25">
-      <c r="A98" s="10" t="s">
+      <c r="A98" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B98" s="19" t="s">
+      <c r="B98" s="15" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="17.25">
-      <c r="A99" s="10" t="s">
+      <c r="A99" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="11" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="100" spans="1:2" ht="17.25">
-      <c r="A100" s="10" t="s">
+      <c r="A100" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="B100" s="19" t="s">
+      <c r="B100" s="15" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="17.25">
-      <c r="A101" s="10" t="s">
+      <c r="A101" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B101" s="19" t="s">
+      <c r="B101" s="15" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="102" spans="1:2" ht="17.25">
-      <c r="A102" s="10" t="s">
+      <c r="A102" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B102" s="19" t="s">
+      <c r="B102" s="15" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="103" spans="1:2" ht="17.25">
-      <c r="A103" s="10" t="s">
+      <c r="A103" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="B103" s="19" t="s">
+      <c r="B103" s="15" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="104" spans="1:2" ht="17.25">
-      <c r="A104" s="10" t="s">
+      <c r="A104" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="B104" s="19" t="s">
+      <c r="B104" s="15" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="105" spans="1:2" ht="17.25">
-      <c r="A105" s="10" t="s">
+      <c r="A105" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B105" s="19" t="s">
+      <c r="B105" s="15" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="106" spans="1:2" ht="17.25">
-      <c r="A106" s="10" t="s">
+      <c r="A106" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B106" s="19" t="s">
+      <c r="B106" s="15" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="107" spans="1:2" ht="17.25">
-      <c r="A107" s="10" t="s">
+      <c r="A107" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B107" s="19" t="s">
+      <c r="B107" s="15" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="108" spans="1:2" ht="17.25">
-      <c r="A108" s="10" t="s">
+      <c r="A108" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B108" s="19" t="s">
+      <c r="B108" s="15" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="109" spans="1:2" ht="17.25">
-      <c r="A109" s="10" t="s">
+      <c r="A109" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="B109" s="19" t="s">
+      <c r="B109" s="15" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="110" spans="1:2" ht="17.25">
-      <c r="A110" s="10" t="s">
+      <c r="A110" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="B110" s="19" t="s">
+      <c r="B110" s="15" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="111" spans="1:2" ht="17.25">
-      <c r="A111" s="10" t="s">
+      <c r="A111" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B111" s="19" t="s">
+      <c r="B111" s="15" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="112" spans="1:2" ht="17.25">
-      <c r="A112" s="10" t="s">
+      <c r="A112" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B112" s="19" t="s">
+      <c r="B112" s="15" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="113" spans="1:2" ht="17.25">
-      <c r="A113" s="10" t="s">
+      <c r="A113" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B113" s="19" t="s">
+      <c r="B113" s="15" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="114" spans="1:2" ht="17.25">
-      <c r="A114" s="10" t="s">
+      <c r="A114" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="B114" s="19" t="s">
+      <c r="B114" s="15" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="115" spans="1:2" ht="17.25">
-      <c r="A115" s="10" t="s">
+      <c r="A115" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B115" s="19" t="b">
+      <c r="B115" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:2" ht="17.25">
-      <c r="A116" s="10" t="s">
+      <c r="A116" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B116" s="15" t="s">
+      <c r="B116" s="11" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="117" spans="1:2" ht="17.25">
-      <c r="A117" s="10" t="s">
+      <c r="A117" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="B117" s="19" t="s">
+      <c r="B117" s="15" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="118" spans="1:2" ht="17.25">
-      <c r="A118" s="10" t="s">
+      <c r="A118" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="B118" s="19">
+      <c r="B118" s="15">
         <v>12013553177</v>
       </c>
     </row>
     <row r="119" spans="1:2" ht="17.25">
-      <c r="A119" s="10" t="s">
+      <c r="A119" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="B119" s="19" t="b">
+      <c r="B119" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:2" ht="16.5">
-      <c r="A120" s="13" t="s">
+      <c r="A120" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="B120" s="13" t="s">
+      <c r="B120" s="9" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="121" spans="1:2" ht="17.25">
-      <c r="A121" s="10" t="s">
+      <c r="A121" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="B121" s="19" t="b">
+      <c r="B121" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:2" ht="17.25">
-      <c r="A122" s="10" t="s">
+      <c r="A122" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="B122" s="15" t="s">
+      <c r="B122" s="11" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="123" spans="1:2" ht="17.25">
-      <c r="A123" s="10" t="s">
+      <c r="A123" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="B123" s="19" t="s">
+      <c r="B123" s="15" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="124" spans="1:2" ht="17.25">
-      <c r="A124" s="10" t="s">
+      <c r="A124" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="B124" s="19" t="s">
+      <c r="B124" s="15" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="125" spans="1:2" ht="17.25">
-      <c r="A125" s="10" t="s">
+      <c r="A125" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="B125" s="19">
+      <c r="B125" s="15">
         <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:2" ht="16.5">
-      <c r="A126" s="13" t="s">
+      <c r="A126" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="B126" s="13" t="s">
+      <c r="B126" s="9" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="127" spans="1:2" ht="17.25">
-      <c r="A127" s="10" t="s">
+      <c r="A127" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B127" s="19" t="s">
+      <c r="B127" s="15" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="128" spans="1:2" ht="17.25">
-      <c r="A128" s="10" t="s">
+      <c r="A128" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B128" s="19" t="s">
+      <c r="B128" s="15" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="129" spans="1:2" ht="16.5">
-      <c r="A129" s="13" t="s">
+      <c r="A129" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="B129" s="13" t="s">
+      <c r="B129" s="9" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="130" spans="1:2" ht="17.25">
-      <c r="A130" s="10" t="s">
+      <c r="A130" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="B130" s="19" t="s">
+      <c r="B130" s="15" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="131" spans="1:2" ht="17.25">
-      <c r="A131" s="10" t="s">
+      <c r="A131" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="B131" s="19" t="s">
+      <c r="B131" s="15" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="132" spans="1:2" ht="17.25">
-      <c r="A132" s="10" t="s">
+      <c r="A132" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="B132" s="19" t="s">
+      <c r="B132" s="15" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="133" spans="1:2" ht="17.25">
-      <c r="A133" s="10" t="s">
+      <c r="A133" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="B133" s="19">
+      <c r="B133" s="15">
         <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:2" ht="17.25">
-      <c r="A134" s="10" t="s">
+      <c r="A134" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="B134" s="19">
+      <c r="B134" s="15">
         <v>2000</v>
       </c>
     </row>
     <row r="135" spans="1:2" ht="17.25">
-      <c r="A135" s="10" t="s">
+      <c r="A135" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="B135" s="19">
+      <c r="B135" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:2" ht="17.25">
-      <c r="A136" s="10" t="s">
+      <c r="A136" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="B136" s="19">
+      <c r="B136" s="15">
         <v>15000</v>
       </c>
     </row>
     <row r="137" spans="1:2" ht="17.25">
-      <c r="A137" s="10" t="s">
+      <c r="A137" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="B137" s="19">
+      <c r="B137" s="15">
         <v>5000</v>
       </c>
     </row>
     <row r="138" spans="1:2" ht="17.25">
-      <c r="A138" s="10" t="s">
+      <c r="A138" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="B138" s="19">
+      <c r="B138" s="15">
         <v>15000</v>
       </c>
     </row>
     <row r="139" spans="1:2" ht="17.25">
-      <c r="A139" s="10" t="s">
+      <c r="A139" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="B139" s="19">
+      <c r="B139" s="15">
         <v>15000</v>
       </c>
     </row>
     <row r="140" spans="1:2" ht="16.5">
-      <c r="A140" s="9" t="s">
+      <c r="A140" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B140" s="9" t="s">
+      <c r="B140" s="5" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="141" spans="1:2" ht="17.25">
-      <c r="A141" s="10" t="s">
+      <c r="A141" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="B141" s="19">
+      <c r="B141" s="15">
         <v>6379</v>
       </c>
     </row>
     <row r="142" spans="1:2" ht="17.25">
-      <c r="A142" s="10" t="s">
+      <c r="A142" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="B142" s="19" t="b">
+      <c r="B142" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:2" ht="17.25">
-      <c r="A143" s="10" t="s">
+      <c r="A143" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="B143" s="19" t="s">
+      <c r="B143" s="15" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="144" spans="1:2" ht="17.25">
-      <c r="A144" s="10" t="s">
+      <c r="A144" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="B144" s="19" t="s">
+      <c r="B144" s="15" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="145" spans="1:2" ht="17.25">
-      <c r="A145" s="10" t="s">
+      <c r="A145" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="B145" s="19" t="s">
+      <c r="B145" s="15" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="146" spans="1:2" ht="17.25">
-      <c r="A146" s="10" t="s">
+      <c r="A146" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="B146" s="19" t="b">
+      <c r="B146" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:2" ht="16.5">
-      <c r="A147" s="9" t="s">
+      <c r="A147" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B147" s="9" t="s">
+      <c r="B147" s="5" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="148" spans="1:2" ht="17.25">
-      <c r="A148" s="10" t="s">
+      <c r="A148" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="B148" s="19">
+      <c r="B148" s="15">
         <v>5000</v>
       </c>
     </row>
     <row r="149" spans="1:2" ht="17.25">
-      <c r="A149" s="10" t="s">
+      <c r="A149" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="B149" s="19">
+      <c r="B149" s="15">
         <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:2" ht="17.25">
-      <c r="A150" s="10" t="s">
+      <c r="A150" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="B150" s="19">
+      <c r="B150" s="15">
         <v>200</v>
       </c>
     </row>
     <row r="151" spans="1:2" ht="17.25">
-      <c r="A151" s="10" t="s">
+      <c r="A151" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="B151" s="19">
+      <c r="B151" s="15">
         <v>5000</v>
       </c>
     </row>
     <row r="152" spans="1:2" ht="17.25">
-      <c r="A152" s="10" t="s">
+      <c r="A152" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="B152" s="19" t="s">
+      <c r="B152" s="15" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="153" spans="1:2" ht="16.5">
-      <c r="A153" s="9" t="s">
+      <c r="A153" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="B153" s="9" t="s">
+      <c r="B153" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="16.5">
-      <c r="A154" s="9" t="s">
+      <c r="A154" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B154" s="9" t="s">
+      <c r="B154" s="5" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="155" spans="1:2" ht="16.5">
-      <c r="A155" s="9" t="s">
+      <c r="A155" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="B155" s="9" t="s">
+      <c r="B155" s="5" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="156" spans="1:2" ht="16.5">
-      <c r="A156" s="9" t="s">
+      <c r="A156" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="B156" s="9" t="s">
+      <c r="B156" s="5" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="157" spans="1:2" ht="17.25">
-      <c r="A157" s="10" t="s">
+      <c r="A157" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="B157" s="19">
+      <c r="B157" s="15">
         <v>15</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="17.25">
-      <c r="A158" s="10" t="s">
+      <c r="A158" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="B158" s="19">
+      <c r="B158" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:2" ht="17.25">
-      <c r="A159" s="10" t="s">
+      <c r="A159" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="B159" s="19">
+      <c r="B159" s="15">
         <v>30000</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="17.25">
-      <c r="A160" s="10" t="s">
+      <c r="A160" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="B160" s="19">
+      <c r="B160" s="15">
         <v>600000</v>
       </c>
     </row>
     <row r="161" spans="1:2" ht="17.25">
-      <c r="A161" s="10" t="s">
+      <c r="A161" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="B161" s="19">
+      <c r="B161" s="15">
         <v>1800000</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="17.25">
-      <c r="A162" s="10" t="s">
+      <c r="A162" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="B162" s="15" t="s">
+      <c r="B162" s="11" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="17.25">
-      <c r="A163" s="10" t="s">
+      <c r="A163" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="B163" s="19" t="s">
+      <c r="B163" s="15" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="17.25">
-      <c r="A164" s="10" t="s">
+      <c r="A164" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="B164" s="15" t="s">
+      <c r="B164" s="11" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="33.75">
-      <c r="A165" s="10" t="s">
+      <c r="A165" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="B165" s="19" t="s">
+      <c r="B165" s="15" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="166" spans="1:2" ht="17.25">
-      <c r="A166" s="10" t="s">
+      <c r="A166" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="B166" s="19">
+      <c r="B166" s="15">
         <v>60</v>
       </c>
     </row>
     <row r="167" spans="1:2" ht="17.25">
-      <c r="A167" s="10" t="s">
+      <c r="A167" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="B167" s="19" t="s">
+      <c r="B167" s="15" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="168" spans="1:2" ht="17.25">
-      <c r="A168" s="10" t="s">
+      <c r="A168" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="B168" s="15" t="s">
+      <c r="B168" s="11" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="169" spans="1:2" ht="17.25">
-      <c r="A169" s="10" t="s">
+      <c r="A169" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="B169" s="19">
+      <c r="B169" s="15">
         <v>60</v>
       </c>
     </row>
     <row r="170" spans="1:2" ht="17.25">
-      <c r="A170" s="10" t="s">
+      <c r="A170" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="B170" s="19" t="s">
+      <c r="B170" s="15" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="171" spans="1:2" ht="17.25">
-      <c r="A171" s="10" t="s">
+      <c r="A171" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="B171" s="19" t="s">
+      <c r="B171" s="15" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="172" spans="1:2" ht="17.25">
-      <c r="A172" s="10" t="s">
+      <c r="A172" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="B172" s="24" t="s">
+      <c r="B172" s="20" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="173" spans="1:2" ht="17.25">
-      <c r="A173" s="10" t="s">
+      <c r="A173" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="B173" s="19" t="s">
+      <c r="B173" s="15" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="174" spans="1:2" ht="17.25">
-      <c r="A174" s="10" t="s">
+      <c r="A174" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="B174" s="19" t="b">
+      <c r="B174" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:2" ht="17.25">
-      <c r="A175" s="10" t="s">
+      <c r="A175" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="B175" s="19" t="b">
+      <c r="B175" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="17.25">
-      <c r="A176" s="10" t="s">
+      <c r="A176" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="B176" s="19" t="s">
+      <c r="B176" s="15" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="177" spans="1:2" ht="17.25">
-      <c r="A177" s="10" t="s">
+      <c r="A177" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="B177" s="19" t="s">
+      <c r="B177" s="15" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="178" spans="1:2" ht="17.25">
-      <c r="A178" s="10" t="s">
+      <c r="A178" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="B178" s="19" t="s">
+      <c r="B178" s="15" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="179" spans="1:2" ht="17.25">
-      <c r="A179" s="10" t="s">
+      <c r="A179" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="B179" s="19" t="s">
+      <c r="B179" s="15" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="180" spans="1:2" ht="17.25">
-      <c r="A180" s="10" t="s">
+      <c r="A180" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="B180" s="19">
+      <c r="B180" s="15">
         <v>4002</v>
       </c>
     </row>
     <row r="181" spans="1:2" ht="17.25">
-      <c r="A181" s="10" t="s">
+      <c r="A181" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="B181" s="19">
+      <c r="B181" s="15">
         <v>1106</v>
       </c>
     </row>
     <row r="182" spans="1:2" ht="17.25">
-      <c r="A182" s="10" t="s">
+      <c r="A182" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="B182" s="15" t="s">
+      <c r="B182" s="11" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="183" spans="1:2" ht="17.25">
-      <c r="A183" s="10" t="s">
+      <c r="A183" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="B183" s="15" t="s">
+      <c r="B183" s="11" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="184" spans="1:2" ht="33.75">
-      <c r="A184" s="10" t="s">
+      <c r="A184" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="B184" s="19" t="s">
+      <c r="B184" s="15" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="185" spans="1:2" ht="17.25">
-      <c r="A185" s="10" t="s">
+      <c r="A185" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="B185" s="19" t="s">
+      <c r="B185" s="15" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="186" spans="1:2" ht="17.25">
-      <c r="A186" s="10" t="s">
+      <c r="A186" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="B186" s="19" t="s">
+      <c r="B186" s="15" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="187" spans="1:2" ht="17.25">
-      <c r="A187" s="10" t="s">
+      <c r="A187" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="B187" s="19" t="s">
+      <c r="B187" s="15" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="188" spans="1:2" ht="17.25">
-      <c r="A188" s="10" t="s">
+      <c r="A188" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="B188" s="19">
+      <c r="B188" s="15">
         <v>30</v>
       </c>
     </row>
     <row r="189" spans="1:2" ht="17.25">
-      <c r="A189" s="10" t="s">
+      <c r="A189" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="B189" s="19" t="s">
+      <c r="B189" s="15" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="190" spans="1:2" ht="17.25">
-      <c r="A190" s="10" t="s">
+      <c r="A190" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="B190" s="19" t="s">
+      <c r="B190" s="15" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="191" spans="1:2" ht="17.25">
-      <c r="A191" s="10" t="s">
+      <c r="A191" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="B191" s="19" t="s">
+      <c r="B191" s="15" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="192" spans="1:2" ht="368.25">
-      <c r="A192" s="10" t="s">
+      <c r="A192" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B192" s="19" t="s">
+      <c r="B192" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="193" spans="1:2" ht="17.25">
-      <c r="A193" s="10" t="s">
+      <c r="A193" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="B193" s="15" t="s">
+      <c r="B193" s="11" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="194" spans="1:2" ht="17.25">
-      <c r="A194" s="10" t="s">
+      <c r="A194" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="B194" s="19" t="s">
+      <c r="B194" s="15" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="195" spans="1:2" ht="17.25">
-      <c r="A195" s="10" t="s">
+      <c r="A195" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="B195" s="19" t="s">
+      <c r="B195" s="15" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="196" spans="1:2" ht="90.75">
-      <c r="A196" s="11" t="s">
+      <c r="A196" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="B196" s="24" t="s">
+      <c r="B196" s="20" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="197" spans="1:2" ht="319.5">
-      <c r="A197" s="11" t="s">
+      <c r="A197" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="B197" s="24" t="s">
+      <c r="B197" s="20" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="198" spans="1:2" ht="17.25">
-      <c r="A198" s="10" t="s">
+      <c r="A198" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="B198" s="19" t="s">
+      <c r="B198" s="15" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="199" spans="1:2" ht="17.25">
-      <c r="A199" s="10" t="s">
+      <c r="A199" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="B199" s="19" t="s">
+      <c r="B199" s="15" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="200" spans="1:2" ht="17.25">
-      <c r="A200" s="10" t="s">
+      <c r="A200" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="B200" s="19" t="s">
+      <c r="B200" s="15" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="201" spans="1:2" ht="16.5">
-      <c r="A201" s="11" t="s">
+      <c r="A201" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="B201" s="19">
+      <c r="B201" s="15">
         <v>3</v>
       </c>
     </row>
     <row r="202" spans="1:2" ht="16.5">
-      <c r="A202" s="11" t="s">
+      <c r="A202" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="B202" s="19">
+      <c r="B202" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:2" ht="16.5">
-      <c r="A203" s="11" t="s">
+      <c r="A203" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="B203" s="19">
+      <c r="B203" s="15">
         <v>3</v>
       </c>
     </row>
     <row r="204" spans="1:2" ht="16.5">
-      <c r="A204" s="11" t="s">
+      <c r="A204" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="B204" s="19">
+      <c r="B204" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="205" spans="1:2" ht="16.5">
-      <c r="A205" s="11" t="s">
+      <c r="A205" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="B205" s="19" t="s">
+      <c r="B205" s="15" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="206" spans="1:2" ht="16.5">
-      <c r="A206" s="11" t="s">
+      <c r="A206" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="B206" s="19">
+      <c r="B206" s="15">
         <v>10</v>
       </c>
     </row>
     <row r="207" spans="1:2" ht="16.5">
-      <c r="A207" s="11" t="s">
+      <c r="A207" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="B207" s="19">
+      <c r="B207" s="15">
         <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:2" ht="16.5">
-      <c r="A208" s="11" t="s">
+      <c r="A208" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="B208" s="19">
+      <c r="B208" s="15">
         <v>24</v>
       </c>
     </row>
     <row r="209" spans="1:2" ht="16.5">
-      <c r="A209" s="11" t="s">
+      <c r="A209" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="B209" s="19">
+      <c r="B209" s="15">
         <v>200</v>
       </c>
     </row>
     <row r="210" spans="1:2" ht="16.5">
-      <c r="A210" s="11" t="s">
+      <c r="A210" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="B210" s="19">
+      <c r="B210" s="15">
         <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:2" ht="16.5">
-      <c r="A211" s="11" t="s">
+      <c r="A211" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="B211" s="19">
+      <c r="B211" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="212" spans="1:2" ht="16.5">
-      <c r="A212" s="11" t="s">
+      <c r="A212" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="B212" s="19">
+      <c r="B212" s="15">
         <v>10</v>
       </c>
     </row>
     <row r="213" spans="1:2" ht="16.5">
-      <c r="A213" s="11" t="s">
+      <c r="A213" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="B213" s="19" t="b">
+      <c r="B213" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="11"/>
-      <c r="B214" s="19"/>
+      <c r="A214" s="7"/>
+      <c r="B214" s="15"/>
     </row>
     <row r="215" spans="1:2" ht="17.25">
-      <c r="A215" s="10" t="s">
+      <c r="A215" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="B215" s="19" t="s">
+      <c r="B215" s="15" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="216" spans="1:2" ht="17.25">
-      <c r="A216" s="10" t="s">
+      <c r="A216" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="B216" s="19" t="s">
+      <c r="B216" s="15" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="217" spans="1:2" ht="17.25">
-      <c r="A217" s="10" t="s">
+      <c r="A217" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="B217" s="19" t="s">
+      <c r="B217" s="15" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="218" spans="1:2" ht="17.25">
-      <c r="A218" s="10" t="s">
+      <c r="A218" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="B218" s="19" t="s">
+      <c r="B218" s="15" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="219" spans="1:2" ht="17.25">
-      <c r="A219" s="10" t="s">
+      <c r="A219" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="B219" s="19" t="s">
+      <c r="B219" s="15" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="220" spans="1:2" ht="17.25">
-      <c r="A220" s="10" t="s">
+      <c r="A220" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="B220" s="19" t="s">
+      <c r="B220" s="15" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="221" spans="1:2" ht="17.25">
-      <c r="A221" s="10" t="s">
+      <c r="A221" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="B221" s="19" t="s">
+      <c r="B221" s="15" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="222" spans="1:2" ht="17.25">
-      <c r="A222" s="10" t="s">
+      <c r="A222" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="B222" s="19">
+      <c r="B222" s="15">
         <v>8400</v>
       </c>
     </row>
     <row r="223" spans="1:2" ht="17.25">
-      <c r="A223" s="10" t="s">
+      <c r="A223" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="B223" s="15" t="s">
+      <c r="B223" s="11" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="224" spans="1:2" ht="17.25">
-      <c r="A224" s="10" t="s">
+      <c r="A224" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="B224" s="19" t="s">
+      <c r="B224" s="15" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="225" spans="1:2" ht="17.25">
-      <c r="A225" s="10" t="s">
+      <c r="A225" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="B225" s="19" t="s">
+      <c r="B225" s="15" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="226" spans="1:2" ht="17.25">
-      <c r="A226" s="10" t="s">
+      <c r="A226" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="B226" s="19" t="s">
+      <c r="B226" s="15" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="227" spans="1:2" ht="17.25">
-      <c r="A227" s="10" t="s">
+      <c r="A227" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="B227" s="19" t="s">
+      <c r="B227" s="15" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="228" spans="1:2" ht="17.25">
-      <c r="A228" s="10" t="s">
+      <c r="A228" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="B228" s="19" t="s">
+      <c r="B228" s="15" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="229" spans="1:2" ht="17.25">
-      <c r="A229" s="10" t="s">
+      <c r="A229" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="B229" s="19" t="s">
+      <c r="B229" s="15" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="230" spans="1:2" ht="17.25">
-      <c r="A230" s="10" t="s">
+      <c r="A230" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="B230" s="19" t="s">
+      <c r="B230" s="15" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="231" spans="1:2" ht="17.25">
-      <c r="A231" s="10" t="s">
+      <c r="A231" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="B231" s="19" t="s">
+      <c r="B231" s="15" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="232" spans="1:2" ht="17.25">
-      <c r="A232" s="10" t="s">
+      <c r="A232" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="B232" s="19" t="s">
+      <c r="B232" s="15" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="233" spans="1:2" ht="17.25">
-      <c r="A233" s="10" t="s">
+      <c r="A233" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="B233" s="19">
+      <c r="B233" s="15">
         <v>60</v>
       </c>
     </row>
     <row r="234" spans="1:2" ht="17.25">
-      <c r="A234" s="10" t="s">
+      <c r="A234" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="B234" s="19" t="s">
+      <c r="B234" s="15" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="235" spans="1:2" ht="17.25">
-      <c r="A235" s="10" t="s">
+      <c r="A235" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="B235" s="19" t="s">
+      <c r="B235" s="15" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="236" spans="1:2" ht="17.25">
-      <c r="A236" s="10" t="s">
+      <c r="A236" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="B236" s="19" t="s">
+      <c r="B236" s="15" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="237" spans="1:2" ht="17.25">
-      <c r="A237" s="10" t="s">
+      <c r="A237" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="B237" s="19">
+      <c r="B237" s="15">
         <v>20</v>
       </c>
     </row>
     <row r="238" spans="1:2" ht="17.25">
-      <c r="A238" s="10" t="s">
+      <c r="A238" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="B238" s="15" t="s">
+      <c r="B238" s="11" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="239" spans="1:2" ht="17.25">
-      <c r="A239" s="10" t="s">
+      <c r="A239" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="B239" s="19" t="s">
+      <c r="B239" s="15" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="240" spans="1:2" ht="17.25">
-      <c r="A240" s="10" t="s">
+      <c r="A240" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="B240" s="15" t="s">
+      <c r="B240" s="11" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="241" spans="1:2" ht="17.25">
-      <c r="A241" s="10" t="s">
+      <c r="A241" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="B241" s="19" t="s">
+      <c r="B241" s="15" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="242" spans="1:2" ht="17.25">
-      <c r="A242" s="10" t="s">
+      <c r="A242" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="B242" s="19" t="s">
+      <c r="B242" s="15" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="243" spans="1:2" ht="16.5">
-      <c r="A243" s="9" t="s">
+      <c r="A243" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="B243" s="9" t="s">
+      <c r="B243" s="5" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="244" spans="1:2" ht="16.5">
-      <c r="A244" s="9" t="s">
+      <c r="A244" s="5" t="s">
         <v>385</v>
       </c>
-      <c r="B244" s="9" t="s">
+      <c r="B244" s="5" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="245" spans="1:2" ht="17.25">
-      <c r="A245" s="10" t="s">
+      <c r="A245" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="B245" s="19" t="s">
+      <c r="B245" s="15" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="246" spans="1:2" ht="17.25">
-      <c r="A246" s="10" t="s">
+      <c r="A246" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="B246" s="19" t="s">
+      <c r="B246" s="15" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="247" spans="1:2" ht="17.25">
-      <c r="A247" s="10" t="s">
+      <c r="A247" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="B247" s="19">
+      <c r="B247" s="15">
         <v>60</v>
       </c>
     </row>
     <row r="248" spans="1:2" ht="17.25">
-      <c r="A248" s="10" t="s">
+      <c r="A248" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="B248" s="19" t="b">
+      <c r="B248" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:2" ht="16.5">
-      <c r="A249" s="9" t="s">
+      <c r="A249" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="B249" s="9" t="s">
+      <c r="B249" s="5" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="250" spans="1:2" ht="16.5">
-      <c r="A250" s="9" t="s">
+      <c r="A250" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="B250" s="9" t="s">
+      <c r="B250" s="5" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="251" spans="1:2" ht="16.5">
-      <c r="A251" s="9" t="s">
+      <c r="A251" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="B251" s="9" t="s">
+      <c r="B251" s="5" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="252" spans="1:2" ht="16.5">
-      <c r="A252" s="9" t="s">
+      <c r="A252" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="B252" s="9" t="s">
+      <c r="B252" s="5" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="253" spans="1:2" ht="16.5">
-      <c r="A253" s="9" t="s">
+      <c r="A253" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="B253" s="9" t="s">
+      <c r="B253" s="5" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="254" spans="1:2" ht="16.5">
-      <c r="A254" s="9" t="s">
+      <c r="A254" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="B254" s="9" t="s">
+      <c r="B254" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="255" spans="1:2" ht="16.5">
-      <c r="A255" s="9" t="s">
+      <c r="A255" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="B255" s="9" t="s">
+      <c r="B255" s="5" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="256" spans="1:2" ht="16.5">
-      <c r="A256" s="9" t="s">
+      <c r="A256" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="B256" s="9" t="s">
+      <c r="B256" s="5" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="257" spans="1:2" ht="16.5">
-      <c r="A257" s="9" t="s">
+      <c r="A257" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="B257" s="9" t="s">
+      <c r="B257" s="5" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="258" spans="1:2" ht="16.5">
-      <c r="A258" s="9" t="s">
+      <c r="A258" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="B258" s="26" t="s">
+      <c r="B258" s="22" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="259" spans="1:2" ht="16.5">
-      <c r="A259" s="9" t="s">
+      <c r="A259" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="B259" s="26" t="s">
+      <c r="B259" s="22" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="260" spans="1:2" ht="16.5">
-      <c r="A260" s="9" t="s">
+      <c r="A260" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="B260" s="26">
+      <c r="B260" s="22">
         <v>1414</v>
       </c>
     </row>
     <row r="261" spans="1:2" ht="16.5">
-      <c r="A261" s="9" t="s">
+      <c r="A261" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="B261" s="26" t="s">
+      <c r="B261" s="22" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="262" spans="1:2" ht="16.5">
-      <c r="A262" s="9" t="s">
+      <c r="A262" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B262" s="26" t="s">
+      <c r="B262" s="22" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="263" spans="1:2" ht="16.5">
-      <c r="A263" s="9" t="s">
+      <c r="A263" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="B263" s="9" t="s">
+      <c r="B263" s="5" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="264" spans="1:2" ht="17.25">
-      <c r="A264" s="10" t="s">
+      <c r="A264" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="B264" s="19" t="s">
+      <c r="B264" s="15" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="265" spans="1:2" ht="16.5">
-      <c r="A265" s="9" t="s">
+      <c r="A265" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="B265" s="26" t="s">
+      <c r="B265" s="22" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="266" spans="1:2" ht="16.5">
-      <c r="A266" s="9" t="s">
+      <c r="A266" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="B266" s="26">
+      <c r="B266" s="22">
         <v>1414</v>
       </c>
     </row>
     <row r="267" spans="1:2" ht="16.5">
-      <c r="A267" s="9" t="s">
+      <c r="A267" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="B267" s="26" t="s">
+      <c r="B267" s="22" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="268" spans="1:2" ht="16.5">
-      <c r="A268" s="9" t="s">
+      <c r="A268" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="B268" s="26" t="s">
+      <c r="B268" s="22" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="269" spans="1:2" ht="16.5">
-      <c r="A269" s="9" t="s">
+      <c r="A269" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="B269" s="26" t="s">
+      <c r="B269" s="22" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="270" spans="1:2" ht="16.5">
-      <c r="A270" s="9" t="s">
+      <c r="A270" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="B270" s="26" t="s">
+      <c r="B270" s="22" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="271" spans="1:2" ht="16.5">
-      <c r="A271" s="9" t="s">
+      <c r="A271" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="B271" s="26" t="s">
+      <c r="B271" s="22" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="272" spans="1:2" ht="16.5">
-      <c r="A272" s="11" t="s">
+      <c r="A272" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="B272" s="19"/>
+      <c r="B272" s="15"/>
     </row>
     <row r="273" spans="1:2" ht="16.5">
-      <c r="A273" s="11" t="s">
+      <c r="A273" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="B273" s="19">
+      <c r="B273" s="15">
         <v>3</v>
       </c>
     </row>
     <row r="274" spans="1:2" ht="16.5">
-      <c r="A274" s="11" t="s">
+      <c r="A274" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="B274" s="19">
+      <c r="B274" s="15">
         <v>500</v>
       </c>
     </row>
     <row r="275" spans="1:2" ht="16.5">
-      <c r="A275" s="11" t="s">
+      <c r="A275" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="B275" s="19">
+      <c r="B275" s="15">
         <v>50</v>
       </c>
     </row>
     <row r="276" spans="1:2" ht="16.5">
-      <c r="A276" s="11" t="s">
+      <c r="A276" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="B276" s="19">
+      <c r="B276" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:2" ht="16.5">
-      <c r="A277" s="11" t="s">
+      <c r="A277" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="B277" s="19">
+      <c r="B277" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:2" ht="16.5">
-      <c r="A278" s="11" t="s">
+      <c r="A278" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="B278" s="19">
+      <c r="B278" s="15">
         <v>30</v>
       </c>
     </row>
     <row r="279" spans="1:2" ht="16.5">
-      <c r="A279" s="11" t="s">
+      <c r="A279" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="B279" s="19"/>
+      <c r="B279" s="15"/>
     </row>
     <row r="280" spans="1:2" ht="16.5">
-      <c r="A280" s="11" t="s">
+      <c r="A280" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="B280" s="19" t="s">
+      <c r="B280" s="15" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="281" spans="1:2" ht="16.5">
-      <c r="A281" s="11" t="s">
+      <c r="A281" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="B281" s="19" t="s">
+      <c r="B281" s="15" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="282" spans="1:2" ht="16.5">
-      <c r="A282" s="11" t="s">
+      <c r="A282" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="B282" s="19" t="s">
+      <c r="B282" s="15" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="283" spans="1:2" ht="16.5">
-      <c r="A283" s="11" t="s">
+      <c r="A283" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="B283" s="19" t="s">
+      <c r="B283" s="15" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="284" spans="1:2" ht="16.5">
-      <c r="A284" s="11" t="s">
+      <c r="A284" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="B284" s="19" t="s">
+      <c r="B284" s="15" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="285" spans="1:2" ht="16.5">
-      <c r="A285" s="11" t="s">
+      <c r="A285" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="B285" s="19" t="s">
+      <c r="B285" s="15" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="286" spans="1:2" ht="16.5">
-      <c r="A286" s="11" t="s">
+      <c r="A286" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="B286" s="19" t="s">
+      <c r="B286" s="15" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="287" spans="1:2" ht="16.5">
-      <c r="A287" s="11" t="s">
+      <c r="A287" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="B287" s="19">
+      <c r="B287" s="15">
         <v>30</v>
       </c>
     </row>
     <row r="288" spans="1:2" ht="16.5">
-      <c r="A288" s="11" t="s">
+      <c r="A288" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="B288" s="19" t="s">
+      <c r="B288" s="15" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="289" spans="1:2" ht="16.5">
-      <c r="A289" s="11" t="s">
+      <c r="A289" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="B289" s="19">
+      <c r="B289" s="15">
         <v>5000</v>
       </c>
     </row>
     <row r="290" spans="1:2" ht="16.5">
-      <c r="A290" s="11" t="s">
+      <c r="A290" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="B290" s="19">
+      <c r="B290" s="15">
         <v>10000</v>
       </c>
     </row>
     <row r="291" spans="1:2" ht="16.5">
-      <c r="A291" s="11" t="s">
+      <c r="A291" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="B291" s="19">
+      <c r="B291" s="15">
         <v>10000</v>
       </c>
     </row>
     <row r="292" spans="1:2" ht="16.5">
-      <c r="A292" s="11" t="s">
+      <c r="A292" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="B292" s="19">
+      <c r="B292" s="15">
         <v>2</v>
       </c>
     </row>
     <row r="293" spans="1:2" ht="16.5">
-      <c r="A293" s="11" t="s">
+      <c r="A293" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="B293" s="19">
+      <c r="B293" s="15">
         <v>300</v>
       </c>
     </row>
     <row r="294" spans="1:2" ht="16.5">
-      <c r="A294" s="11" t="s">
+      <c r="A294" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="B294" s="19">
+      <c r="B294" s="15">
         <v>0.3</v>
       </c>
     </row>
     <row r="295" spans="1:2" ht="16.5">
-      <c r="A295" s="11" t="s">
+      <c r="A295" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="B295" s="19">
+      <c r="B295" s="15">
         <v>16</v>
       </c>
     </row>
     <row r="296" spans="1:2" ht="16.5">
-      <c r="A296" s="11" t="s">
+      <c r="A296" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="B296" s="19">
+      <c r="B296" s="15">
         <v>40</v>
       </c>
     </row>
     <row r="297" spans="1:2" ht="16.5">
-      <c r="A297" s="11" t="s">
+      <c r="A297" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="B297" s="19">
+      <c r="B297" s="15">
         <v>100</v>
       </c>
     </row>
     <row r="298" spans="1:2" ht="16.5">
-      <c r="A298" s="11" t="s">
+      <c r="A298" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="B298" s="19">
+      <c r="B298" s="15">
         <v>30</v>
       </c>
     </row>
     <row r="299" spans="1:2" ht="16.5">
-      <c r="A299" s="11" t="s">
+      <c r="A299" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="B299" s="19">
+      <c r="B299" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="300" spans="1:2" ht="16.5">
-      <c r="A300" s="11" t="s">
+      <c r="A300" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="B300" s="19">
+      <c r="B300" s="15">
         <v>500</v>
       </c>
     </row>
     <row r="301" spans="1:2" ht="16.5">
-      <c r="A301" s="11" t="s">
+      <c r="A301" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="B301" s="19">
+      <c r="B301" s="15">
         <v>500</v>
       </c>
     </row>
     <row r="302" spans="1:2" ht="16.5">
-      <c r="A302" s="11" t="s">
+      <c r="A302" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="B302" s="19">
+      <c r="B302" s="15">
         <v>4</v>
       </c>
     </row>
     <row r="303" spans="1:2" ht="16.5">
-      <c r="A303" s="11" t="s">
+      <c r="A303" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="B303" s="19">
+      <c r="B303" s="15">
         <v>4</v>
       </c>
     </row>
     <row r="304" spans="1:2" ht="16.5">
-      <c r="A304" s="11" t="s">
+      <c r="A304" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="B304" s="19" t="s">
+      <c r="B304" s="15" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="305" spans="1:2" ht="16.5">
-      <c r="A305" s="11" t="s">
+      <c r="A305" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="B305" s="24" t="s">
+      <c r="B305" s="20" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="306" spans="1:2" ht="16.5">
-      <c r="A306" s="11" t="s">
+      <c r="A306" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="B306" s="19">
+      <c r="B306" s="15">
         <v>20</v>
       </c>
     </row>
     <row r="307" spans="1:2" ht="16.5">
-      <c r="A307" s="11" t="s">
+      <c r="A307" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="B307" s="19">
+      <c r="B307" s="15">
         <v>60</v>
       </c>
     </row>
     <row r="308" spans="1:2" ht="16.5">
-      <c r="A308" s="11" t="s">
+      <c r="A308" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="B308" s="19" t="b">
+      <c r="B308" s="15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="309" spans="1:2" ht="16.5">
-      <c r="A309" s="11" t="s">
+      <c r="A309" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="B309" s="19">
+      <c r="B309" s="15">
         <v>60000</v>
       </c>
     </row>
     <row r="310" spans="1:2" ht="16.5">
-      <c r="A310" s="9" t="s">
+      <c r="A310" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="B310" s="21"/>
+      <c r="B310" s="17"/>
     </row>
     <row r="311" spans="1:2" ht="16.5">
-      <c r="A311" s="11" t="s">
+      <c r="A311" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="B311" s="11" t="s">
+      <c r="B311" s="7" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="312" spans="1:2" ht="16.5">
-      <c r="A312" s="11" t="s">
+      <c r="A312" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="B312" s="11" t="s">
+      <c r="B312" s="7" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="313" spans="1:2" ht="16.5">
-      <c r="A313" s="9" t="s">
+      <c r="A313" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="B313" s="21"/>
+      <c r="B313" s="17"/>
     </row>
     <row r="314" spans="1:2" ht="16.5">
-      <c r="A314" s="9" t="s">
+      <c r="A314" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="B314" s="21"/>
-    </row>
-    <row r="315" spans="1:2">
-      <c r="A315" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="B315" s="8" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="316" spans="1:2">
-      <c r="A316" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="B316" s="6" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="317" spans="1:2">
-      <c r="A317" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="B317" s="8" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="318" spans="1:2">
-      <c r="A318" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="B318" s="6" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="319" spans="1:2">
-      <c r="A319" s="7" t="s">
-        <v>452</v>
-      </c>
-      <c r="B319" s="8" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="320" spans="1:2">
-      <c r="A320" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="B320" s="6" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="321" spans="1:2">
-      <c r="A321" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="B321" s="8" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="322" spans="1:2">
-      <c r="A322" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="B322" s="6" t="s">
-        <v>449</v>
-      </c>
+      <c r="B314" s="17"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B26" r:id="rId1" xr:uid="{FFFAC64A-4879-4B8C-B0B0-FB962A579855}"/>
-    <hyperlink ref="B240" r:id="rId2" xr:uid="{8D07B395-99F7-47F9-8425-1501F85DF496}"/>
-    <hyperlink ref="B238" r:id="rId3" xr:uid="{5F8FCB46-8995-4C68-B555-3BE36D83F4E7}"/>
-    <hyperlink ref="B223" r:id="rId4" xr:uid="{D08B209F-7FFB-430D-9819-2A8069BBE435}"/>
-    <hyperlink ref="B193" r:id="rId5" xr:uid="{98EEEE0A-9C53-46E8-A5C4-194D05BA5AB8}"/>
-    <hyperlink ref="B183" r:id="rId6" xr:uid="{C3BA8EEC-3A4B-46E8-9EB7-EAD38BEB923C}"/>
-    <hyperlink ref="B182" r:id="rId7" xr:uid="{6453665D-FA30-4B54-8A68-D1DB1C72443B}"/>
-    <hyperlink ref="B10" r:id="rId8" xr:uid="{3A1B200D-660D-4589-B463-E6FCE43A5CE7}"/>
-    <hyperlink ref="B20" r:id="rId9" xr:uid="{C7D190A5-E531-4C07-8639-D0A00F754CE2}"/>
-    <hyperlink ref="B23" r:id="rId10" xr:uid="{05269187-9A97-4014-854A-DA17E10D4EC2}"/>
-    <hyperlink ref="B24" r:id="rId11" xr:uid="{1D9A726E-F303-41BF-9F77-356FB79E49D8}"/>
-    <hyperlink ref="B32" r:id="rId12" xr:uid="{4CB30951-BA4C-4AA5-98E9-43EB24CACDFC}"/>
-    <hyperlink ref="B33" r:id="rId13" xr:uid="{A20C92B0-F3C3-4D06-BD48-265711319DC7}"/>
-    <hyperlink ref="B34" r:id="rId14" xr:uid="{9E16AB6C-F916-4AD7-858B-8BFBC224E692}"/>
-    <hyperlink ref="B35" r:id="rId15" xr:uid="{5D84C5C8-E8A4-4949-A245-EA0793DAECDD}"/>
-    <hyperlink ref="B37" r:id="rId16" xr:uid="{0B11C022-41AB-4859-806F-F0EA5CD619B6}"/>
-    <hyperlink ref="B39" r:id="rId17" xr:uid="{78EA58EC-ED60-4828-B34F-24CA685943F6}"/>
-    <hyperlink ref="B40" r:id="rId18" xr:uid="{4924B128-6EE6-4207-A221-C1EA51C00B4E}"/>
-    <hyperlink ref="B41" r:id="rId19" xr:uid="{630A7E79-B76C-41AB-9658-66D26247F08A}"/>
-    <hyperlink ref="B42" r:id="rId20" xr:uid="{F5E1C23B-6597-4A98-8FD4-F138C2258528}"/>
-    <hyperlink ref="B45" r:id="rId21" xr:uid="{F39B83D7-294A-4FBD-83DF-5C9E230644B1}"/>
-    <hyperlink ref="B46" r:id="rId22" xr:uid="{27EFEA26-ECB5-461E-8AAD-7215FA70030D}"/>
-    <hyperlink ref="B47" r:id="rId23" xr:uid="{379767AD-43C5-4CCB-B094-B43B18F5FDC3}"/>
-    <hyperlink ref="B48" r:id="rId24" xr:uid="{89E2A8D2-B383-4E7F-9D86-36B83F03D07E}"/>
-    <hyperlink ref="B49" r:id="rId25" xr:uid="{0A4E9F7C-01EA-4897-AFF5-7216C5CF9651}"/>
-    <hyperlink ref="B57" r:id="rId26" xr:uid="{AF76C251-35A4-4D6A-B15C-98999053C364}"/>
-    <hyperlink ref="B58" r:id="rId27" xr:uid="{65C0F940-2A25-4A00-BC23-B9BE92C45250}"/>
-    <hyperlink ref="B61" r:id="rId28" xr:uid="{F5AF51FF-A0C6-473E-9996-F138CD5C4EC1}"/>
-    <hyperlink ref="B67" r:id="rId29" xr:uid="{47ACB6A0-07F6-492D-BB6A-A5EC74C10FB3}"/>
-    <hyperlink ref="B68" r:id="rId30" xr:uid="{4AAEC545-5B2F-417C-B652-3646705D59A2}"/>
-    <hyperlink ref="B87" r:id="rId31" xr:uid="{B708596F-07FD-4E2D-94CF-81D73727D193}"/>
-    <hyperlink ref="B91" r:id="rId32" xr:uid="{7A40CC19-E5E3-488D-8FDF-92F65823517F}"/>
-    <hyperlink ref="B92" r:id="rId33" xr:uid="{52206BCD-8E42-42E5-893E-ED0D40F62B0B}"/>
-    <hyperlink ref="B99" r:id="rId34" xr:uid="{A3649783-22B5-4B61-BFCD-96B5D4BBA901}"/>
-    <hyperlink ref="B116" r:id="rId35" xr:uid="{7EAFF5F4-FC8E-4C41-9C33-157A04C060FC}"/>
-    <hyperlink ref="B120" r:id="rId36" xr:uid="{E7085CDB-DA35-4AC2-B983-5ADD51675F08}"/>
-    <hyperlink ref="B122" r:id="rId37" xr:uid="{8FAD2A70-6652-41AC-86D9-E02D0EEF4D8D}"/>
-    <hyperlink ref="B129" r:id="rId38" xr:uid="{C6C0F9F0-9E1C-491E-AD27-13AEABF489E7}"/>
-    <hyperlink ref="B162" r:id="rId39" xr:uid="{8C70ADD7-F5D6-4EA7-B069-743D460DA3C5}"/>
-    <hyperlink ref="B164" r:id="rId40" xr:uid="{03DD17D4-6236-41E3-B028-C72A41994E7D}"/>
-    <hyperlink ref="B168" r:id="rId41" xr:uid="{0B23B679-A85E-4278-8964-13DBC0422A75}"/>
+    <hyperlink ref="B26" r:id="rId1" xr:uid="{26AD130E-062D-45D6-A39C-B5EDAE874F52}"/>
+    <hyperlink ref="B240" r:id="rId2" xr:uid="{87A1747F-709D-46C6-BEC9-91E856F384BC}"/>
+    <hyperlink ref="B238" r:id="rId3" xr:uid="{4787CEEB-5E0E-46FC-88C3-5550FAB46287}"/>
+    <hyperlink ref="B223" r:id="rId4" xr:uid="{7F10031D-DB99-482B-B942-220CC06FE8BE}"/>
+    <hyperlink ref="B193" r:id="rId5" xr:uid="{62D78C59-3874-4B16-9F68-C54A3E44867F}"/>
+    <hyperlink ref="B183" r:id="rId6" xr:uid="{34172045-A216-4C48-9D8C-3356807020CA}"/>
+    <hyperlink ref="B182" r:id="rId7" xr:uid="{7C7EDF8C-D48A-4186-847B-077967891E03}"/>
+    <hyperlink ref="B10" r:id="rId8" xr:uid="{6F63FA36-08F8-4366-AB9F-5171748DBD83}"/>
+    <hyperlink ref="B20" r:id="rId9" xr:uid="{FE9A82CF-FE2C-45FA-8058-6761359B84C0}"/>
+    <hyperlink ref="B23" r:id="rId10" xr:uid="{A58689FD-C8A8-47C2-A018-62B33EA1D9D1}"/>
+    <hyperlink ref="B24" r:id="rId11" xr:uid="{17C16446-6543-41E9-8F3C-BBC160507E27}"/>
+    <hyperlink ref="B32" r:id="rId12" xr:uid="{170C4756-AC5B-44D0-97AD-4F1BE7FD6EA3}"/>
+    <hyperlink ref="B33" r:id="rId13" xr:uid="{332898E8-AED9-45C6-8C2E-B7226170BDAE}"/>
+    <hyperlink ref="B34" r:id="rId14" xr:uid="{EA82BCBB-5C2F-4C2D-8983-48DB748F2F82}"/>
+    <hyperlink ref="B35" r:id="rId15" xr:uid="{5A5810E6-C953-4324-B6E8-BBBD477A3B7F}"/>
+    <hyperlink ref="B37" r:id="rId16" xr:uid="{65441EA9-0D16-4D3A-B2D8-031187551D79}"/>
+    <hyperlink ref="B39" r:id="rId17" xr:uid="{8074E186-237D-4A3A-A530-FD38CAA1E78D}"/>
+    <hyperlink ref="B40" r:id="rId18" xr:uid="{9C385D5D-61BA-42B4-9866-A09B11F5B730}"/>
+    <hyperlink ref="B41" r:id="rId19" xr:uid="{EFBE9CDD-A0C9-46E0-90CB-C2F0DB04E93C}"/>
+    <hyperlink ref="B42" r:id="rId20" xr:uid="{5F786DF3-2293-45F7-88C8-5E234DB45DE5}"/>
+    <hyperlink ref="B45" r:id="rId21" xr:uid="{F5A00FAB-641A-47FB-8F72-ACD3360F92CB}"/>
+    <hyperlink ref="B46" r:id="rId22" xr:uid="{7329D06A-567D-4096-B1BB-76416F76748E}"/>
+    <hyperlink ref="B47" r:id="rId23" xr:uid="{0AA8F9F1-5150-4163-8744-E99F59918CBC}"/>
+    <hyperlink ref="B48" r:id="rId24" xr:uid="{ACDAB384-14CD-4AA9-AC37-929BEF417827}"/>
+    <hyperlink ref="B49" r:id="rId25" xr:uid="{64E246F2-1D65-49FD-89D2-B45C95002D89}"/>
+    <hyperlink ref="B57" r:id="rId26" xr:uid="{464B66F0-28B6-4105-A7EE-C833B881EB32}"/>
+    <hyperlink ref="B58" r:id="rId27" xr:uid="{1AB8D35E-0368-4EC9-BC5A-E4290A48011B}"/>
+    <hyperlink ref="B61" r:id="rId28" xr:uid="{93CBB2C0-C5A0-4BD0-A3F4-9EAEBB4E7937}"/>
+    <hyperlink ref="B67" r:id="rId29" xr:uid="{71619D19-FFD4-4758-B7B9-57812313F1D2}"/>
+    <hyperlink ref="B68" r:id="rId30" xr:uid="{74B6DAA4-4BEA-4843-A8E2-6E0B2B02B559}"/>
+    <hyperlink ref="B87" r:id="rId31" xr:uid="{1DFCAC30-32E1-4310-9864-B04E90D07797}"/>
+    <hyperlink ref="B91" r:id="rId32" xr:uid="{22B630F6-D3A8-470A-B9F7-0ABB3FE6C81B}"/>
+    <hyperlink ref="B92" r:id="rId33" xr:uid="{F0900423-4ACA-4783-9D9B-D91932AFB0B5}"/>
+    <hyperlink ref="B99" r:id="rId34" xr:uid="{982205D8-1B7F-4F04-8D7B-B1837CBAA306}"/>
+    <hyperlink ref="B116" r:id="rId35" xr:uid="{2A42859E-3895-4FB1-9418-EEC88BEC57A5}"/>
+    <hyperlink ref="B120" r:id="rId36" xr:uid="{D90E3D1E-D06F-4845-96EB-AE714E4BE59D}"/>
+    <hyperlink ref="B122" r:id="rId37" xr:uid="{A8AF0D17-C62E-4B77-915F-873BFEBA037D}"/>
+    <hyperlink ref="B129" r:id="rId38" xr:uid="{44F78BE3-7681-4D26-A602-2B94C2C9D7DC}"/>
+    <hyperlink ref="B162" r:id="rId39" xr:uid="{F3A03B30-037F-4BB3-AB0D-F9BCEF0E6BFC}"/>
+    <hyperlink ref="B164" r:id="rId40" xr:uid="{E8FFCF7F-3477-4D79-B2EA-2F3EAED78658}"/>
+    <hyperlink ref="B168" r:id="rId41" xr:uid="{810FCECE-BE9A-4B1F-822F-06C487E0C120}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7172,50 +7075,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B2" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B3" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B4" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B5" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B6" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
